--- a/research/traditional_assets/database/data/peru/peru_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_electrical_equipment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1169666146812001</v>
+        <v>0.1166532881678906</v>
       </c>
       <c r="C2">
-        <v>221.9901372503063</v>
+        <v>220.5888516040493</v>
       </c>
       <c r="D2">
-        <v>185.5901372503063</v>
+        <v>186.4108516040493</v>
       </c>
       <c r="E2">
-        <v>-1.2</v>
+        <v>1.022</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.222</v>
       </c>
       <c r="G2">
         <v>36.4</v>
@@ -1451,28 +1451,28 @@
         <v>21.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1117666</v>
       </c>
       <c r="N2">
-        <v>21.5</v>
+        <v>21.3882334</v>
       </c>
       <c r="O2">
-        <v>6.342499999999999</v>
+        <v>6.309528853</v>
       </c>
       <c r="P2">
-        <v>15.1575</v>
+        <v>15.078704547</v>
       </c>
       <c r="Q2">
-        <v>18.6575</v>
+        <v>18.578704547</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1169666146812001</v>
+        <v>0.1174734072402935</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.108764815132331</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>192.3651609693773</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1166532881678906</v>
+        <v>0.116339961654581</v>
       </c>
       <c r="C3">
-        <v>220.5888516040493</v>
+        <v>219.1948569049618</v>
       </c>
       <c r="D3">
-        <v>186.4108516040493</v>
+        <v>187.2388569049618</v>
       </c>
       <c r="E3">
-        <v>1.022</v>
+        <v>3.244</v>
       </c>
       <c r="F3">
-        <v>2.222</v>
+        <v>4.444</v>
       </c>
       <c r="G3">
         <v>36.4</v>
@@ -1533,28 +1533,28 @@
         <v>21.5</v>
       </c>
       <c r="M3">
-        <v>0.1117666</v>
+        <v>0.2235332</v>
       </c>
       <c r="N3">
-        <v>21.3882334</v>
+        <v>21.2764668</v>
       </c>
       <c r="O3">
-        <v>6.309528853</v>
+        <v>6.276557706</v>
       </c>
       <c r="P3">
-        <v>15.078704547</v>
+        <v>14.999909094</v>
       </c>
       <c r="Q3">
-        <v>18.578704547</v>
+        <v>18.499909094</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1174734072402935</v>
+        <v>0.1179905425046745</v>
       </c>
       <c r="T3">
-        <v>1.108764815132331</v>
+        <v>1.116764733203583</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.3651609693773</v>
+        <v>96.18258048468864</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.116339961654581</v>
+        <v>0.1160266351412715</v>
       </c>
       <c r="C4">
-        <v>219.1948569049618</v>
+        <v>217.8082507419595</v>
       </c>
       <c r="D4">
-        <v>187.2388569049618</v>
+        <v>188.0742507419594</v>
       </c>
       <c r="E4">
-        <v>3.244</v>
+        <v>5.465999999999999</v>
       </c>
       <c r="F4">
-        <v>4.444</v>
+        <v>6.665999999999999</v>
       </c>
       <c r="G4">
         <v>36.4</v>
@@ -1615,28 +1615,28 @@
         <v>21.5</v>
       </c>
       <c r="M4">
-        <v>0.2235332</v>
+        <v>0.3352998</v>
       </c>
       <c r="N4">
-        <v>21.2764668</v>
+        <v>21.1647002</v>
       </c>
       <c r="O4">
-        <v>6.276557706</v>
+        <v>6.243586559</v>
       </c>
       <c r="P4">
-        <v>14.999909094</v>
+        <v>14.921113641</v>
       </c>
       <c r="Q4">
-        <v>18.499909094</v>
+        <v>18.421113641</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1179905425046745</v>
+        <v>0.1185183403518263</v>
       </c>
       <c r="T4">
-        <v>1.116764733203583</v>
+        <v>1.124929598039191</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.18258048468864</v>
+        <v>64.12172032312574</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1160266351412715</v>
+        <v>0.1157133086279619</v>
       </c>
       <c r="C5">
-        <v>217.8082507419595</v>
+        <v>216.4291324533925</v>
       </c>
       <c r="D5">
-        <v>188.0742507419594</v>
+        <v>188.9171324533925</v>
       </c>
       <c r="E5">
-        <v>5.465999999999999</v>
+        <v>7.688</v>
       </c>
       <c r="F5">
-        <v>6.665999999999999</v>
+        <v>8.888</v>
       </c>
       <c r="G5">
         <v>36.4</v>
@@ -1697,28 +1697,28 @@
         <v>21.5</v>
       </c>
       <c r="M5">
-        <v>0.3352998</v>
+        <v>0.4470664</v>
       </c>
       <c r="N5">
-        <v>21.1647002</v>
+        <v>21.0529336</v>
       </c>
       <c r="O5">
-        <v>6.243586559</v>
+        <v>6.210615411999999</v>
       </c>
       <c r="P5">
-        <v>14.921113641</v>
+        <v>14.842318188</v>
       </c>
       <c r="Q5">
-        <v>18.421113641</v>
+        <v>18.342318188</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1185183403518263</v>
+        <v>0.1190571339874603</v>
       </c>
       <c r="T5">
-        <v>1.124929598039191</v>
+        <v>1.13326456422554</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.12172032312574</v>
+        <v>48.09129024234431</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1157133086279619</v>
+        <v>0.1153999821146524</v>
       </c>
       <c r="C6">
-        <v>216.4291324533925</v>
+        <v>215.0576031664244</v>
       </c>
       <c r="D6">
-        <v>188.9171324533925</v>
+        <v>189.7676031664244</v>
       </c>
       <c r="E6">
-        <v>7.688</v>
+        <v>9.91</v>
       </c>
       <c r="F6">
-        <v>8.888</v>
+        <v>11.11</v>
       </c>
       <c r="G6">
         <v>36.4</v>
@@ -1779,28 +1779,28 @@
         <v>21.5</v>
       </c>
       <c r="M6">
-        <v>0.4470664</v>
+        <v>0.5588329999999999</v>
       </c>
       <c r="N6">
-        <v>21.0529336</v>
+        <v>20.941167</v>
       </c>
       <c r="O6">
-        <v>6.210615411999999</v>
+        <v>6.177644265</v>
       </c>
       <c r="P6">
-        <v>14.842318188</v>
+        <v>14.763522735</v>
       </c>
       <c r="Q6">
-        <v>18.342318188</v>
+        <v>18.263522735</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1190571339874603</v>
+        <v>0.1196072706470025</v>
       </c>
       <c r="T6">
-        <v>1.13326456422554</v>
+        <v>1.141775003384234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.09129024234431</v>
+        <v>38.47303219387545</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1153999821146524</v>
+        <v>0.1150866556013428</v>
       </c>
       <c r="C7">
-        <v>215.0576031664244</v>
+        <v>213.6937658374784</v>
       </c>
       <c r="D7">
-        <v>189.7676031664244</v>
+        <v>190.6257658374784</v>
       </c>
       <c r="E7">
-        <v>9.91</v>
+        <v>12.132</v>
       </c>
       <c r="F7">
-        <v>11.11</v>
+        <v>13.332</v>
       </c>
       <c r="G7">
         <v>36.4</v>
@@ -1861,28 +1861,28 @@
         <v>21.5</v>
       </c>
       <c r="M7">
-        <v>0.5588329999999999</v>
+        <v>0.6705996</v>
       </c>
       <c r="N7">
-        <v>20.941167</v>
+        <v>20.8294004</v>
       </c>
       <c r="O7">
-        <v>6.177644265</v>
+        <v>6.144673118</v>
       </c>
       <c r="P7">
-        <v>14.763522735</v>
+        <v>14.684727282</v>
       </c>
       <c r="Q7">
-        <v>18.263522735</v>
+        <v>18.184727282</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1196072706470025</v>
+        <v>0.1201691123418541</v>
       </c>
       <c r="T7">
-        <v>1.141775003384234</v>
+        <v>1.150466515716517</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.47303219387545</v>
+        <v>32.06086016156288</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1150866556013428</v>
+        <v>0.1147733290880333</v>
       </c>
       <c r="C8">
-        <v>213.6937658374784</v>
+        <v>212.3377252937862</v>
       </c>
       <c r="D8">
-        <v>190.6257658374784</v>
+        <v>191.4917252937862</v>
       </c>
       <c r="E8">
-        <v>12.132</v>
+        <v>14.354</v>
       </c>
       <c r="F8">
-        <v>13.332</v>
+        <v>15.554</v>
       </c>
       <c r="G8">
         <v>36.4</v>
@@ -1943,28 +1943,28 @@
         <v>21.5</v>
       </c>
       <c r="M8">
-        <v>0.6705996</v>
+        <v>0.7823661999999998</v>
       </c>
       <c r="N8">
-        <v>20.8294004</v>
+        <v>20.7176338</v>
       </c>
       <c r="O8">
-        <v>6.144673118</v>
+        <v>6.111701971</v>
       </c>
       <c r="P8">
-        <v>14.684727282</v>
+        <v>14.605931829</v>
       </c>
       <c r="Q8">
-        <v>18.184727282</v>
+        <v>18.105931829</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1201691123418541</v>
+        <v>0.1207430366537993</v>
       </c>
       <c r="T8">
-        <v>1.150466515716517</v>
+        <v>1.159344942292505</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.06086016156288</v>
+        <v>27.48073728133962</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1147733290880333</v>
+        <v>0.1144600025747238</v>
       </c>
       <c r="C9">
-        <v>212.3377252937862</v>
+        <v>210.9895882760753</v>
       </c>
       <c r="D9">
-        <v>191.4917252937862</v>
+        <v>192.3655882760753</v>
       </c>
       <c r="E9">
-        <v>14.354</v>
+        <v>16.576</v>
       </c>
       <c r="F9">
-        <v>15.554</v>
+        <v>17.776</v>
       </c>
       <c r="G9">
         <v>36.4</v>
@@ -2025,28 +2025,28 @@
         <v>21.5</v>
       </c>
       <c r="M9">
-        <v>0.7823662</v>
+        <v>0.8941327999999999</v>
       </c>
       <c r="N9">
-        <v>20.7176338</v>
+        <v>20.6058672</v>
       </c>
       <c r="O9">
-        <v>6.111701971</v>
+        <v>6.078730823999999</v>
       </c>
       <c r="P9">
-        <v>14.605931829</v>
+        <v>14.527136376</v>
       </c>
       <c r="Q9">
-        <v>18.105931829</v>
+        <v>18.027136376</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1207430366537993</v>
+        <v>0.1213294375812215</v>
       </c>
       <c r="T9">
-        <v>1.159344942292505</v>
+        <v>1.168416378141884</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.48073728133961</v>
+        <v>24.04564512117216</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1144600025747238</v>
+        <v>0.1141466760614142</v>
       </c>
       <c r="C10">
-        <v>210.9895882760753</v>
+        <v>209.6494634824296</v>
       </c>
       <c r="D10">
-        <v>192.3655882760753</v>
+        <v>193.2474634824295</v>
       </c>
       <c r="E10">
-        <v>16.576</v>
+        <v>18.798</v>
       </c>
       <c r="F10">
-        <v>17.776</v>
+        <v>19.998</v>
       </c>
       <c r="G10">
         <v>36.4</v>
@@ -2107,28 +2107,28 @@
         <v>21.5</v>
       </c>
       <c r="M10">
-        <v>0.8941327999999999</v>
+        <v>1.0058994</v>
       </c>
       <c r="N10">
-        <v>20.6058672</v>
+        <v>20.4941006</v>
       </c>
       <c r="O10">
-        <v>6.078730823999999</v>
+        <v>6.045759676999999</v>
       </c>
       <c r="P10">
-        <v>14.527136376</v>
+        <v>14.448340923</v>
       </c>
       <c r="Q10">
-        <v>18.027136376</v>
+        <v>17.948340923</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1213294375812215</v>
+        <v>0.1219287264411145</v>
       </c>
       <c r="T10">
-        <v>1.168416378141884</v>
+        <v>1.177687186207733</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.04564512117216</v>
+        <v>21.37390677437525</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1141466760614142</v>
+        <v>0.1138333495481047</v>
       </c>
       <c r="C11">
-        <v>209.6494634824296</v>
+        <v>208.3174616133616</v>
       </c>
       <c r="D11">
-        <v>193.2474634824295</v>
+        <v>194.1374616133616</v>
       </c>
       <c r="E11">
-        <v>18.798</v>
+        <v>21.02</v>
       </c>
       <c r="F11">
-        <v>19.998</v>
+        <v>22.22</v>
       </c>
       <c r="G11">
         <v>36.4</v>
@@ -2189,28 +2189,28 @@
         <v>21.5</v>
       </c>
       <c r="M11">
-        <v>1.0058994</v>
+        <v>1.117666</v>
       </c>
       <c r="N11">
-        <v>20.4941006</v>
+        <v>20.382334</v>
       </c>
       <c r="O11">
-        <v>6.045759676999999</v>
+        <v>6.01278853</v>
       </c>
       <c r="P11">
-        <v>14.448340923</v>
+        <v>14.36954547</v>
       </c>
       <c r="Q11">
-        <v>17.948340923</v>
+        <v>17.86954547</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1219287264411145</v>
+        <v>0.1225413328312275</v>
       </c>
       <c r="T11">
-        <v>1.177687186207733</v>
+        <v>1.187164012230601</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.37390677437525</v>
+        <v>19.23651609693773</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1138333495481047</v>
+        <v>0.1135200230347952</v>
       </c>
       <c r="C12">
-        <v>208.3174616133616</v>
+        <v>206.9936954181379</v>
       </c>
       <c r="D12">
-        <v>194.1374616133616</v>
+        <v>195.0356954181379</v>
       </c>
       <c r="E12">
-        <v>21.02</v>
+        <v>23.242</v>
       </c>
       <c r="F12">
-        <v>22.22</v>
+        <v>24.442</v>
       </c>
       <c r="G12">
         <v>36.4</v>
@@ -2271,28 +2271,28 @@
         <v>21.5</v>
       </c>
       <c r="M12">
-        <v>1.117666</v>
+        <v>1.2294326</v>
       </c>
       <c r="N12">
-        <v>20.382334</v>
+        <v>20.2705674</v>
       </c>
       <c r="O12">
-        <v>6.01278853</v>
+        <v>5.979817383</v>
       </c>
       <c r="P12">
-        <v>14.36954547</v>
+        <v>14.290750017</v>
       </c>
       <c r="Q12">
-        <v>17.86954547</v>
+        <v>17.790750017</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1225413328312275</v>
+        <v>0.1231677056570732</v>
       </c>
       <c r="T12">
-        <v>1.187164012230601</v>
+        <v>1.196853800636005</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.23651609693773</v>
+        <v>17.48774190630703</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1135200230347952</v>
+        <v>0.1132066965214856</v>
       </c>
       <c r="C13">
-        <v>206.9936954181379</v>
+        <v>205.678279742394</v>
       </c>
       <c r="D13">
-        <v>195.0356954181379</v>
+        <v>195.942279742394</v>
       </c>
       <c r="E13">
-        <v>23.242</v>
+        <v>25.464</v>
       </c>
       <c r="F13">
-        <v>24.442</v>
+        <v>26.664</v>
       </c>
       <c r="G13">
         <v>36.4</v>
@@ -2353,28 +2353,28 @@
         <v>21.5</v>
       </c>
       <c r="M13">
-        <v>1.2294326</v>
+        <v>1.3411992</v>
       </c>
       <c r="N13">
-        <v>20.2705674</v>
+        <v>20.1588008</v>
       </c>
       <c r="O13">
-        <v>5.979817383</v>
+        <v>5.946846236</v>
       </c>
       <c r="P13">
-        <v>14.290750017</v>
+        <v>14.211954564</v>
       </c>
       <c r="Q13">
-        <v>17.790750017</v>
+        <v>17.711954564</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1231677056570732</v>
+        <v>0.1238083142289609</v>
       </c>
       <c r="T13">
-        <v>1.196853800636005</v>
+        <v>1.206763811505168</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.48774190630703</v>
+        <v>16.03043008078144</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1132066965214856</v>
+        <v>0.1128933700081761</v>
       </c>
       <c r="C14">
-        <v>205.678279742394</v>
+        <v>204.3713315770853</v>
       </c>
       <c r="D14">
-        <v>195.942279742394</v>
+        <v>196.8573315770853</v>
       </c>
       <c r="E14">
-        <v>25.464</v>
+        <v>27.686</v>
       </c>
       <c r="F14">
-        <v>26.664</v>
+        <v>28.886</v>
       </c>
       <c r="G14">
         <v>36.4</v>
@@ -2435,28 +2435,28 @@
         <v>21.5</v>
       </c>
       <c r="M14">
-        <v>1.3411992</v>
+        <v>1.4529658</v>
       </c>
       <c r="N14">
-        <v>20.1588008</v>
+        <v>20.0470342</v>
       </c>
       <c r="O14">
-        <v>5.946846236</v>
+        <v>5.913875088999999</v>
       </c>
       <c r="P14">
-        <v>14.211954564</v>
+        <v>14.133159111</v>
       </c>
       <c r="Q14">
-        <v>17.711954564</v>
+        <v>17.633159111</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1238083142289609</v>
+        <v>0.1244636494346852</v>
       </c>
       <c r="T14">
-        <v>1.206763811505168</v>
+        <v>1.216901638716151</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.03043008078144</v>
+        <v>14.79732007456748</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1128933700081761</v>
+        <v>0.1125800434948665</v>
       </c>
       <c r="C15">
-        <v>204.3713315770853</v>
+        <v>203.0729701088154</v>
       </c>
       <c r="D15">
-        <v>196.8573315770853</v>
+        <v>197.7809701088154</v>
       </c>
       <c r="E15">
-        <v>27.686</v>
+        <v>29.908</v>
       </c>
       <c r="F15">
-        <v>28.886</v>
+        <v>31.108</v>
       </c>
       <c r="G15">
         <v>36.4</v>
@@ -2517,28 +2517,28 @@
         <v>21.5</v>
       </c>
       <c r="M15">
-        <v>1.4529658</v>
+        <v>1.5647324</v>
       </c>
       <c r="N15">
-        <v>20.0470342</v>
+        <v>19.9352676</v>
       </c>
       <c r="O15">
-        <v>5.913875088999999</v>
+        <v>5.880903942</v>
       </c>
       <c r="P15">
-        <v>14.133159111</v>
+        <v>14.054363658</v>
       </c>
       <c r="Q15">
-        <v>17.633159111</v>
+        <v>17.554363658</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1244636494346852</v>
+        <v>0.1251342249940309</v>
       </c>
       <c r="T15">
-        <v>1.216901638716151</v>
+        <v>1.227275229350645</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.79732007456748</v>
+        <v>13.7403686406698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1125800434948665</v>
+        <v>0.112425341981557</v>
       </c>
       <c r="C16">
-        <v>203.0729701088154</v>
+        <v>201.3102100086741</v>
       </c>
       <c r="D16">
-        <v>197.7809701088154</v>
+        <v>198.2402100086741</v>
       </c>
       <c r="E16">
-        <v>29.908</v>
+        <v>32.13</v>
       </c>
       <c r="F16">
-        <v>31.108</v>
+        <v>33.33000000000001</v>
       </c>
       <c r="G16">
         <v>36.4</v>
@@ -2599,45 +2599,45 @@
         <v>21.5</v>
       </c>
       <c r="M16">
-        <v>1.5647324</v>
+        <v>1.726494</v>
       </c>
       <c r="N16">
-        <v>19.9352676</v>
+        <v>19.773506</v>
       </c>
       <c r="O16">
-        <v>5.880903942</v>
+        <v>5.83318427</v>
       </c>
       <c r="P16">
-        <v>14.054363658</v>
+        <v>13.94032173</v>
       </c>
       <c r="Q16">
-        <v>17.554363658</v>
+        <v>17.44032173</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1251342249940309</v>
+        <v>0.1258205788018318</v>
       </c>
       <c r="T16">
-        <v>1.227275229350645</v>
+        <v>1.237892904470657</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.295</v>
       </c>
       <c r="W16">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.7403686406698</v>
+        <v>12.45298275001245</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.112425341981557</v>
+        <v>0.1121225904682475</v>
       </c>
       <c r="C17">
-        <v>201.3102100086741</v>
+        <v>199.9931433527307</v>
       </c>
       <c r="D17">
-        <v>198.2402100086741</v>
+        <v>199.1451433527307</v>
       </c>
       <c r="E17">
-        <v>32.13</v>
+        <v>34.352</v>
       </c>
       <c r="F17">
-        <v>33.33</v>
+        <v>35.552</v>
       </c>
       <c r="G17">
         <v>36.4</v>
@@ -2681,28 +2681,28 @@
         <v>21.5</v>
       </c>
       <c r="M17">
-        <v>1.726494</v>
+        <v>1.8415936</v>
       </c>
       <c r="N17">
-        <v>19.773506</v>
+        <v>19.6584064</v>
       </c>
       <c r="O17">
-        <v>5.83318427</v>
+        <v>5.799229888</v>
       </c>
       <c r="P17">
-        <v>13.94032173</v>
+        <v>13.859176512</v>
       </c>
       <c r="Q17">
-        <v>17.44032173</v>
+        <v>17.359176512</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1258205788018318</v>
+        <v>0.1265232743669613</v>
       </c>
       <c r="T17">
-        <v>1.237892904470657</v>
+        <v>1.248763381379241</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.45298275001245</v>
+        <v>11.67467132813668</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1121225904682475</v>
+        <v>0.1118198389549379</v>
       </c>
       <c r="C18">
-        <v>199.9931433527307</v>
+        <v>198.6843763213757</v>
       </c>
       <c r="D18">
-        <v>199.1451433527307</v>
+        <v>200.0583763213757</v>
       </c>
       <c r="E18">
-        <v>34.352</v>
+        <v>36.574</v>
       </c>
       <c r="F18">
-        <v>35.552</v>
+        <v>37.774</v>
       </c>
       <c r="G18">
         <v>36.4</v>
@@ -2763,28 +2763,28 @@
         <v>21.5</v>
       </c>
       <c r="M18">
-        <v>1.8415936</v>
+        <v>1.9566932</v>
       </c>
       <c r="N18">
-        <v>19.6584064</v>
+        <v>19.5433068</v>
       </c>
       <c r="O18">
-        <v>5.799229888</v>
+        <v>5.765275506</v>
       </c>
       <c r="P18">
-        <v>13.859176512</v>
+        <v>13.778031294</v>
       </c>
       <c r="Q18">
-        <v>17.359176512</v>
+        <v>17.278031294</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1265232743669613</v>
+        <v>0.1272429023553469</v>
       </c>
       <c r="T18">
-        <v>1.248763381379241</v>
+        <v>1.259895797490441</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.67467132813668</v>
+        <v>10.98792595589334</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1118198389549379</v>
+        <v>0.1115170874416284</v>
       </c>
       <c r="C19">
-        <v>198.6843763213757</v>
+        <v>197.3840236210274</v>
       </c>
       <c r="D19">
-        <v>200.0583763213757</v>
+        <v>200.9800236210274</v>
       </c>
       <c r="E19">
-        <v>36.574</v>
+        <v>38.796</v>
       </c>
       <c r="F19">
-        <v>37.774</v>
+        <v>39.996</v>
       </c>
       <c r="G19">
         <v>36.4</v>
@@ -2845,28 +2845,28 @@
         <v>21.5</v>
       </c>
       <c r="M19">
-        <v>1.9566932</v>
+        <v>2.0717928</v>
       </c>
       <c r="N19">
-        <v>19.5433068</v>
+        <v>19.4282072</v>
       </c>
       <c r="O19">
-        <v>5.765275506</v>
+        <v>5.731321123999999</v>
       </c>
       <c r="P19">
-        <v>13.778031294</v>
+        <v>13.696886076</v>
       </c>
       <c r="Q19">
-        <v>17.278031294</v>
+        <v>17.196886076</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1272429023553469</v>
+        <v>0.1279800822458883</v>
       </c>
       <c r="T19">
-        <v>1.259895797490441</v>
+        <v>1.271299735945816</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.98792595589334</v>
+        <v>10.37748562501038</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1115170874416284</v>
+        <v>0.1112143359283188</v>
       </c>
       <c r="C20">
-        <v>197.3840236210273</v>
+        <v>196.0922020816468</v>
       </c>
       <c r="D20">
-        <v>200.9800236210273</v>
+        <v>201.9102020816468</v>
       </c>
       <c r="E20">
-        <v>38.79599999999999</v>
+        <v>41.01799999999999</v>
       </c>
       <c r="F20">
-        <v>39.996</v>
+        <v>42.218</v>
       </c>
       <c r="G20">
         <v>36.4</v>
@@ -2927,28 +2927,28 @@
         <v>21.5</v>
       </c>
       <c r="M20">
-        <v>2.0717928</v>
+        <v>2.1868924</v>
       </c>
       <c r="N20">
-        <v>19.4282072</v>
+        <v>19.3131076</v>
       </c>
       <c r="O20">
-        <v>5.731321123999999</v>
+        <v>5.697366742000001</v>
       </c>
       <c r="P20">
-        <v>13.696886076</v>
+        <v>13.615740858</v>
       </c>
       <c r="Q20">
-        <v>17.196886076</v>
+        <v>17.115740858</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1279800822458883</v>
+        <v>0.1287354641090356</v>
       </c>
       <c r="T20">
-        <v>1.271299735945816</v>
+        <v>1.282985253128485</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.37748562501038</v>
+        <v>9.831302171062465</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1112143359283188</v>
+        <v>0.1111512844150093</v>
       </c>
       <c r="C21">
-        <v>196.0922020816468</v>
+        <v>194.0650068801729</v>
       </c>
       <c r="D21">
-        <v>201.9102020816468</v>
+        <v>202.1050068801729</v>
       </c>
       <c r="E21">
-        <v>41.01799999999999</v>
+        <v>43.23999999999999</v>
       </c>
       <c r="F21">
-        <v>42.218</v>
+        <v>44.44</v>
       </c>
       <c r="G21">
         <v>36.4</v>
@@ -3009,45 +3009,45 @@
         <v>21.5</v>
       </c>
       <c r="M21">
-        <v>2.1868924</v>
+        <v>2.37754</v>
       </c>
       <c r="N21">
-        <v>19.3131076</v>
+        <v>19.12246</v>
       </c>
       <c r="O21">
-        <v>5.697366742000001</v>
+        <v>5.6411257</v>
       </c>
       <c r="P21">
-        <v>13.615740858</v>
+        <v>13.4813343</v>
       </c>
       <c r="Q21">
-        <v>17.115740858</v>
+        <v>16.9813343</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1287354641090356</v>
+        <v>0.1295097305187616</v>
       </c>
       <c r="T21">
-        <v>1.282985253128485</v>
+        <v>1.294962908240721</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.295</v>
       </c>
       <c r="W21">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.831302171062465</v>
+        <v>9.042960370803437</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1111512844150093</v>
+        <v>0.1108605179016998</v>
       </c>
       <c r="C22">
-        <v>194.0650068801729</v>
+        <v>192.7462485091703</v>
       </c>
       <c r="D22">
-        <v>202.1050068801729</v>
+        <v>203.0082485091703</v>
       </c>
       <c r="E22">
-        <v>43.23999999999999</v>
+        <v>45.462</v>
       </c>
       <c r="F22">
-        <v>44.44</v>
+        <v>46.662</v>
       </c>
       <c r="G22">
         <v>36.4</v>
@@ -3091,28 +3091,28 @@
         <v>21.5</v>
       </c>
       <c r="M22">
-        <v>2.37754</v>
+        <v>2.496417</v>
       </c>
       <c r="N22">
-        <v>19.12246</v>
+        <v>19.003583</v>
       </c>
       <c r="O22">
-        <v>5.6411257</v>
+        <v>5.606056984999999</v>
       </c>
       <c r="P22">
-        <v>13.4813343</v>
+        <v>13.397526015</v>
       </c>
       <c r="Q22">
-        <v>16.9813343</v>
+        <v>16.897526015</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1295097305187616</v>
+        <v>0.1303035986097465</v>
       </c>
       <c r="T22">
-        <v>1.294962908240721</v>
+        <v>1.30724379512795</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.042960370803437</v>
+        <v>8.612343210288985</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1108605179016998</v>
+        <v>0.1105697513883902</v>
       </c>
       <c r="C23">
-        <v>192.7462485091703</v>
+        <v>191.4355998626459</v>
       </c>
       <c r="D23">
-        <v>203.0082485091703</v>
+        <v>203.9195998626459</v>
       </c>
       <c r="E23">
-        <v>45.462</v>
+        <v>47.684</v>
       </c>
       <c r="F23">
-        <v>46.662</v>
+        <v>48.884</v>
       </c>
       <c r="G23">
         <v>36.4</v>
@@ -3173,28 +3173,28 @@
         <v>21.5</v>
       </c>
       <c r="M23">
-        <v>2.496417</v>
+        <v>2.615294</v>
       </c>
       <c r="N23">
-        <v>19.003583</v>
+        <v>18.884706</v>
       </c>
       <c r="O23">
-        <v>5.606056984999999</v>
+        <v>5.57098827</v>
       </c>
       <c r="P23">
-        <v>13.397526015</v>
+        <v>13.31371773</v>
       </c>
       <c r="Q23">
-        <v>16.897526015</v>
+        <v>16.81371773</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1303035986097465</v>
+        <v>0.131117822292808</v>
       </c>
       <c r="T23">
-        <v>1.30724379512795</v>
+        <v>1.319839576550749</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.612343210288985</v>
+        <v>8.22087306436676</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1105697513883902</v>
+        <v>0.1102789848750807</v>
       </c>
       <c r="C24">
-        <v>191.4355998626459</v>
+        <v>190.133170652453</v>
       </c>
       <c r="D24">
-        <v>203.9195998626459</v>
+        <v>204.839170652453</v>
       </c>
       <c r="E24">
-        <v>47.684</v>
+        <v>49.906</v>
       </c>
       <c r="F24">
-        <v>48.884</v>
+        <v>51.106</v>
       </c>
       <c r="G24">
         <v>36.4</v>
@@ -3255,28 +3255,28 @@
         <v>21.5</v>
       </c>
       <c r="M24">
-        <v>2.615294</v>
+        <v>2.734171</v>
       </c>
       <c r="N24">
-        <v>18.884706</v>
+        <v>18.765829</v>
       </c>
       <c r="O24">
-        <v>5.57098827</v>
+        <v>5.535919555</v>
       </c>
       <c r="P24">
-        <v>13.31371773</v>
+        <v>13.229909445</v>
       </c>
       <c r="Q24">
-        <v>16.81371773</v>
+        <v>16.729909445</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.131117822292808</v>
+        <v>0.1319531946429619</v>
       </c>
       <c r="T24">
-        <v>1.319839576550749</v>
+        <v>1.332762521127386</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.22087306436676</v>
+        <v>7.86344380069864</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1102789848750807</v>
+        <v>0.1101235783617712</v>
       </c>
       <c r="C25">
-        <v>190.133170652453</v>
+        <v>188.4060644707241</v>
       </c>
       <c r="D25">
-        <v>204.839170652453</v>
+        <v>205.3340644707241</v>
       </c>
       <c r="E25">
-        <v>49.906</v>
+        <v>52.128</v>
       </c>
       <c r="F25">
-        <v>51.106</v>
+        <v>53.328</v>
       </c>
       <c r="G25">
         <v>36.4</v>
@@ -3337,45 +3337,45 @@
         <v>21.5</v>
       </c>
       <c r="M25">
-        <v>2.734171</v>
+        <v>2.8957104</v>
       </c>
       <c r="N25">
-        <v>18.765829</v>
+        <v>18.6042896</v>
       </c>
       <c r="O25">
-        <v>5.535919555</v>
+        <v>5.488265432</v>
       </c>
       <c r="P25">
-        <v>13.229909445</v>
+        <v>13.116024168</v>
       </c>
       <c r="Q25">
-        <v>16.729909445</v>
+        <v>16.616024168</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1319531946429619</v>
+        <v>0.1328105504760147</v>
       </c>
       <c r="T25">
-        <v>1.332762521127386</v>
+        <v>1.346025543192883</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.295</v>
       </c>
       <c r="W25">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.86344380069864</v>
+        <v>7.424775626733944</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1101235783617712</v>
+        <v>0.1098384518484616</v>
       </c>
       <c r="C26">
-        <v>188.4060644707241</v>
+        <v>187.098299343309</v>
       </c>
       <c r="D26">
-        <v>205.3340644707241</v>
+        <v>206.248299343309</v>
       </c>
       <c r="E26">
-        <v>52.12799999999999</v>
+        <v>54.34999999999999</v>
       </c>
       <c r="F26">
-        <v>53.328</v>
+        <v>55.55</v>
       </c>
       <c r="G26">
         <v>36.4</v>
@@ -3419,28 +3419,28 @@
         <v>21.5</v>
       </c>
       <c r="M26">
-        <v>2.8957104</v>
+        <v>3.016365</v>
       </c>
       <c r="N26">
-        <v>18.6042896</v>
+        <v>18.483635</v>
       </c>
       <c r="O26">
-        <v>5.488265432</v>
+        <v>5.452672325</v>
       </c>
       <c r="P26">
-        <v>13.116024168</v>
+        <v>13.030962675</v>
       </c>
       <c r="Q26">
-        <v>16.616024168</v>
+        <v>16.530962675</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1328105504760147</v>
+        <v>0.1336907691312821</v>
       </c>
       <c r="T26">
-        <v>1.346025543192883</v>
+        <v>1.359642245846793</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.424775626733944</v>
+        <v>7.127784601664587</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1098384518484616</v>
+        <v>0.1095533253351521</v>
       </c>
       <c r="C27">
-        <v>187.098299343309</v>
+        <v>185.798711753307</v>
       </c>
       <c r="D27">
-        <v>206.248299343309</v>
+        <v>207.170711753307</v>
       </c>
       <c r="E27">
-        <v>54.34999999999999</v>
+        <v>56.572</v>
       </c>
       <c r="F27">
-        <v>55.55</v>
+        <v>57.772</v>
       </c>
       <c r="G27">
         <v>36.4</v>
@@ -3501,28 +3501,28 @@
         <v>21.5</v>
       </c>
       <c r="M27">
-        <v>3.016365</v>
+        <v>3.1370196</v>
       </c>
       <c r="N27">
-        <v>18.483635</v>
+        <v>18.3629804</v>
       </c>
       <c r="O27">
-        <v>5.452672325</v>
+        <v>5.417079218</v>
       </c>
       <c r="P27">
-        <v>13.030962675</v>
+        <v>12.945901182</v>
       </c>
       <c r="Q27">
-        <v>16.530962675</v>
+        <v>16.445901182</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1336907691312821</v>
+        <v>0.1345947774799352</v>
       </c>
       <c r="T27">
-        <v>1.359642245846793</v>
+        <v>1.373626967491349</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.127784601664587</v>
+        <v>6.853639040062103</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1095533253351521</v>
+        <v>0.1092681988218425</v>
       </c>
       <c r="C28">
-        <v>185.798711753307</v>
+        <v>184.5074119117893</v>
       </c>
       <c r="D28">
-        <v>207.170711753307</v>
+        <v>208.1014119117893</v>
       </c>
       <c r="E28">
-        <v>56.572</v>
+        <v>58.794</v>
       </c>
       <c r="F28">
-        <v>57.772</v>
+        <v>59.994</v>
       </c>
       <c r="G28">
         <v>36.4</v>
@@ -3583,28 +3583,28 @@
         <v>21.5</v>
       </c>
       <c r="M28">
-        <v>3.1370196</v>
+        <v>3.2576742</v>
       </c>
       <c r="N28">
-        <v>18.3629804</v>
+        <v>18.2423258</v>
       </c>
       <c r="O28">
-        <v>5.417079218</v>
+        <v>5.381486111</v>
       </c>
       <c r="P28">
-        <v>12.945901182</v>
+        <v>12.860839689</v>
       </c>
       <c r="Q28">
-        <v>16.445901182</v>
+        <v>16.360839689</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1345947774799352</v>
+        <v>0.1355235531806062</v>
       </c>
       <c r="T28">
-        <v>1.373626967491349</v>
+        <v>1.38799483219466</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.853639040062103</v>
+        <v>6.599800557096839</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1092681988218425</v>
+        <v>0.108983072308533</v>
       </c>
       <c r="C29">
-        <v>184.5074119117893</v>
+        <v>183.2245120192273</v>
       </c>
       <c r="D29">
-        <v>208.1014119117893</v>
+        <v>209.0405120192273</v>
       </c>
       <c r="E29">
-        <v>58.794</v>
+        <v>61.016</v>
       </c>
       <c r="F29">
-        <v>59.994</v>
+        <v>62.216</v>
       </c>
       <c r="G29">
         <v>36.4</v>
@@ -3665,28 +3665,28 @@
         <v>21.5</v>
       </c>
       <c r="M29">
-        <v>3.2576742</v>
+        <v>3.3783288</v>
       </c>
       <c r="N29">
-        <v>18.2423258</v>
+        <v>18.1216712</v>
       </c>
       <c r="O29">
-        <v>5.381486111</v>
+        <v>5.345893004000001</v>
       </c>
       <c r="P29">
-        <v>12.860839689</v>
+        <v>12.775778196</v>
       </c>
       <c r="Q29">
-        <v>16.360839689</v>
+        <v>16.275778196</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1355235531806062</v>
+        <v>0.1364781282062958</v>
       </c>
       <c r="T29">
-        <v>1.38799483219466</v>
+        <v>1.402761804250841</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.599800557096839</v>
+        <v>6.364093394343381</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.108983072308533</v>
+        <v>0.1086979457952234</v>
       </c>
       <c r="C30">
-        <v>183.2245120192273</v>
+        <v>181.9501263105831</v>
       </c>
       <c r="D30">
-        <v>209.0405120192273</v>
+        <v>209.9881263105831</v>
       </c>
       <c r="E30">
-        <v>61.016</v>
+        <v>63.238</v>
       </c>
       <c r="F30">
-        <v>62.216</v>
+        <v>64.438</v>
       </c>
       <c r="G30">
         <v>36.4</v>
@@ -3747,28 +3747,28 @@
         <v>21.5</v>
       </c>
       <c r="M30">
-        <v>3.3783288</v>
+        <v>3.4989834</v>
       </c>
       <c r="N30">
-        <v>18.1216712</v>
+        <v>18.0010166</v>
       </c>
       <c r="O30">
-        <v>5.345893004000001</v>
+        <v>5.310299896999999</v>
       </c>
       <c r="P30">
-        <v>12.775778196</v>
+        <v>12.690716703</v>
       </c>
       <c r="Q30">
-        <v>16.275778196</v>
+        <v>16.190716703</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1364781282062958</v>
+        <v>0.1374595926693288</v>
       </c>
       <c r="T30">
-        <v>1.402761804250841</v>
+        <v>1.417944747350858</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.364093394343381</v>
+        <v>6.144641897986712</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1086979457952234</v>
+        <v>0.1086243192819139</v>
       </c>
       <c r="C31">
-        <v>181.9501263105831</v>
+        <v>179.9742203988816</v>
       </c>
       <c r="D31">
-        <v>209.9881263105831</v>
+        <v>210.2342203988815</v>
       </c>
       <c r="E31">
-        <v>63.23799999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="F31">
-        <v>64.43799999999999</v>
+        <v>66.66</v>
       </c>
       <c r="G31">
         <v>36.4</v>
@@ -3829,45 +3829,45 @@
         <v>21.5</v>
       </c>
       <c r="M31">
-        <v>3.498983399999999</v>
+        <v>3.686298</v>
       </c>
       <c r="N31">
-        <v>18.0010166</v>
+        <v>17.813702</v>
       </c>
       <c r="O31">
-        <v>5.310299896999999</v>
+        <v>5.25504209</v>
       </c>
       <c r="P31">
-        <v>12.690716703</v>
+        <v>12.55865991</v>
       </c>
       <c r="Q31">
-        <v>16.190716703</v>
+        <v>16.05865991</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1374595926693288</v>
+        <v>0.1384690989741627</v>
       </c>
       <c r="T31">
-        <v>1.417944747350858</v>
+        <v>1.433561488825161</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.295</v>
       </c>
       <c r="W31">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.144641897986713</v>
+        <v>5.832409642410895</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1086243192819139</v>
+        <v>0.1083462427686043</v>
       </c>
       <c r="C32">
-        <v>179.9742203988816</v>
+        <v>178.686908021976</v>
       </c>
       <c r="D32">
-        <v>210.2342203988815</v>
+        <v>211.168908021976</v>
       </c>
       <c r="E32">
-        <v>65.45999999999999</v>
+        <v>67.68199999999999</v>
       </c>
       <c r="F32">
-        <v>66.66</v>
+        <v>68.88199999999999</v>
       </c>
       <c r="G32">
         <v>36.4</v>
@@ -3911,28 +3911,28 @@
         <v>21.5</v>
       </c>
       <c r="M32">
-        <v>3.686298</v>
+        <v>3.8091746</v>
       </c>
       <c r="N32">
-        <v>17.813702</v>
+        <v>17.6908254</v>
       </c>
       <c r="O32">
-        <v>5.25504209</v>
+        <v>5.218793493</v>
       </c>
       <c r="P32">
-        <v>12.55865991</v>
+        <v>12.472031907</v>
       </c>
       <c r="Q32">
-        <v>16.05865991</v>
+        <v>15.972031907</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1384690989741627</v>
+        <v>0.1395078663313107</v>
       </c>
       <c r="T32">
-        <v>1.433561488825161</v>
+        <v>1.449630889472632</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.832409642410895</v>
+        <v>5.644267395881513</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1083462427686043</v>
+        <v>0.1080681662552948</v>
       </c>
       <c r="C33">
-        <v>178.686908021976</v>
+        <v>177.407943881124</v>
       </c>
       <c r="D33">
-        <v>211.168908021976</v>
+        <v>212.111943881124</v>
       </c>
       <c r="E33">
-        <v>67.68199999999999</v>
+        <v>69.904</v>
       </c>
       <c r="F33">
-        <v>68.88199999999999</v>
+        <v>71.104</v>
       </c>
       <c r="G33">
         <v>36.4</v>
@@ -3993,28 +3993,28 @@
         <v>21.5</v>
       </c>
       <c r="M33">
-        <v>3.8091746</v>
+        <v>3.9320512</v>
       </c>
       <c r="N33">
-        <v>17.6908254</v>
+        <v>17.5679488</v>
       </c>
       <c r="O33">
-        <v>5.218793493</v>
+        <v>5.182544896</v>
       </c>
       <c r="P33">
-        <v>12.472031907</v>
+        <v>12.385403904</v>
       </c>
       <c r="Q33">
-        <v>15.972031907</v>
+        <v>15.885403904</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1395078663313107</v>
+        <v>0.1405771856695512</v>
       </c>
       <c r="T33">
-        <v>1.449630889472632</v>
+        <v>1.466172919550912</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.644267395881513</v>
+        <v>5.467884039760214</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1080681662552948</v>
+        <v>0.1077900897419853</v>
       </c>
       <c r="C34">
-        <v>177.407943881124</v>
+        <v>176.1374403224305</v>
       </c>
       <c r="D34">
-        <v>212.111943881124</v>
+        <v>213.0634403224305</v>
       </c>
       <c r="E34">
-        <v>69.904</v>
+        <v>72.12599999999999</v>
       </c>
       <c r="F34">
-        <v>71.104</v>
+        <v>73.32599999999999</v>
       </c>
       <c r="G34">
         <v>36.4</v>
@@ -4075,28 +4075,28 @@
         <v>21.5</v>
       </c>
       <c r="M34">
-        <v>3.9320512</v>
+        <v>4.0549278</v>
       </c>
       <c r="N34">
-        <v>17.5679488</v>
+        <v>17.4450722</v>
       </c>
       <c r="O34">
-        <v>5.182544896</v>
+        <v>5.146296298999999</v>
       </c>
       <c r="P34">
-        <v>12.385403904</v>
+        <v>12.298775901</v>
       </c>
       <c r="Q34">
-        <v>15.885403904</v>
+        <v>15.798775901</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1405771856695512</v>
+        <v>0.1416784249880377</v>
       </c>
       <c r="T34">
-        <v>1.466172919550912</v>
+        <v>1.483208741571826</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.467884039760214</v>
+        <v>5.302190584009905</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1077900897419853</v>
+        <v>0.1075120132286757</v>
       </c>
       <c r="C35">
-        <v>176.1374403224305</v>
+        <v>174.8755117169425</v>
       </c>
       <c r="D35">
-        <v>213.0634403224305</v>
+        <v>214.0235117169425</v>
       </c>
       <c r="E35">
-        <v>72.12599999999999</v>
+        <v>74.348</v>
       </c>
       <c r="F35">
-        <v>73.32599999999999</v>
+        <v>75.548</v>
       </c>
       <c r="G35">
         <v>36.4</v>
@@ -4157,28 +4157,28 @@
         <v>21.5</v>
       </c>
       <c r="M35">
-        <v>4.0549278</v>
+        <v>4.1778044</v>
       </c>
       <c r="N35">
-        <v>17.4450722</v>
+        <v>17.3221956</v>
       </c>
       <c r="O35">
-        <v>5.146296298999999</v>
+        <v>5.110047702</v>
       </c>
       <c r="P35">
-        <v>12.298775901</v>
+        <v>12.212147898</v>
       </c>
       <c r="Q35">
-        <v>15.798775901</v>
+        <v>15.712147898</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1416784249880377</v>
+        <v>0.1428130351949632</v>
       </c>
       <c r="T35">
-        <v>1.483208741571826</v>
+        <v>1.500760800623678</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.302190584009905</v>
+        <v>5.146243802127261</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1075120132286757</v>
+        <v>0.1072339367153662</v>
       </c>
       <c r="C36">
-        <v>174.8755117169425</v>
+        <v>173.6222745064777</v>
       </c>
       <c r="D36">
-        <v>214.0235117169425</v>
+        <v>214.9922745064777</v>
       </c>
       <c r="E36">
-        <v>74.348</v>
+        <v>76.57000000000001</v>
       </c>
       <c r="F36">
-        <v>75.548</v>
+        <v>77.77000000000001</v>
       </c>
       <c r="G36">
         <v>36.4</v>
@@ -4239,28 +4239,28 @@
         <v>21.5</v>
       </c>
       <c r="M36">
-        <v>4.1778044</v>
+        <v>4.300681000000001</v>
       </c>
       <c r="N36">
-        <v>17.3221956</v>
+        <v>17.199319</v>
       </c>
       <c r="O36">
-        <v>5.110047702</v>
+        <v>5.073799104999999</v>
       </c>
       <c r="P36">
-        <v>12.212147898</v>
+        <v>12.125519895</v>
       </c>
       <c r="Q36">
-        <v>15.712147898</v>
+        <v>15.625519895</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1428130351949632</v>
+        <v>0.1439825564851788</v>
       </c>
       <c r="T36">
-        <v>1.500760800623678</v>
+        <v>1.518852923030971</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.146243802127261</v>
+        <v>4.999208264923624</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1072339367153662</v>
+        <v>0.1069558602020566</v>
       </c>
       <c r="C37">
-        <v>173.6222745064777</v>
+        <v>172.3778472507041</v>
       </c>
       <c r="D37">
-        <v>214.9922745064777</v>
+        <v>215.9698472507041</v>
       </c>
       <c r="E37">
-        <v>76.57000000000001</v>
+        <v>78.792</v>
       </c>
       <c r="F37">
-        <v>77.77000000000001</v>
+        <v>79.992</v>
       </c>
       <c r="G37">
         <v>36.4</v>
@@ -4321,28 +4321,28 @@
         <v>21.5</v>
       </c>
       <c r="M37">
-        <v>4.300681000000001</v>
+        <v>4.423557600000001</v>
       </c>
       <c r="N37">
-        <v>17.199319</v>
+        <v>17.0764424</v>
       </c>
       <c r="O37">
-        <v>5.073799104999999</v>
+        <v>5.037550507999999</v>
       </c>
       <c r="P37">
-        <v>12.125519895</v>
+        <v>12.038891892</v>
       </c>
       <c r="Q37">
-        <v>15.625519895</v>
+        <v>15.538891892</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1439825564851788</v>
+        <v>0.1451886253157135</v>
       </c>
       <c r="T37">
-        <v>1.518852923030971</v>
+        <v>1.537510424263491</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.999208264923624</v>
+        <v>4.860341368675746</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1069558602020567</v>
+        <v>0.1066777836887471</v>
       </c>
       <c r="C38">
-        <v>172.3778472507041</v>
+        <v>171.1423506755089</v>
       </c>
       <c r="D38">
-        <v>215.9698472507041</v>
+        <v>216.9563506755088</v>
       </c>
       <c r="E38">
-        <v>78.79199999999999</v>
+        <v>81.014</v>
       </c>
       <c r="F38">
-        <v>79.99199999999999</v>
+        <v>82.214</v>
       </c>
       <c r="G38">
         <v>36.4</v>
@@ -4403,28 +4403,28 @@
         <v>21.5</v>
       </c>
       <c r="M38">
-        <v>4.4235576</v>
+        <v>4.5464342</v>
       </c>
       <c r="N38">
-        <v>17.0764424</v>
+        <v>16.9535658</v>
       </c>
       <c r="O38">
-        <v>5.037550508</v>
+        <v>5.001301911</v>
       </c>
       <c r="P38">
-        <v>12.038891892</v>
+        <v>11.952263889</v>
       </c>
       <c r="Q38">
-        <v>15.538891892</v>
+        <v>15.452263889</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1451886253157135</v>
+        <v>0.1464329820456303</v>
       </c>
       <c r="T38">
-        <v>1.537510424263491</v>
+        <v>1.556760227122441</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.860341368675747</v>
+        <v>4.72898079114397</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1066777836887471</v>
+        <v>0.1063997071754376</v>
       </c>
       <c r="C39">
-        <v>171.1423506755089</v>
+        <v>169.9159077226996</v>
       </c>
       <c r="D39">
-        <v>216.9563506755088</v>
+        <v>217.9519077226996</v>
       </c>
       <c r="E39">
-        <v>81.014</v>
+        <v>83.23599999999999</v>
       </c>
       <c r="F39">
-        <v>82.214</v>
+        <v>84.43599999999999</v>
       </c>
       <c r="G39">
         <v>36.4</v>
@@ -4485,28 +4485,28 @@
         <v>21.5</v>
       </c>
       <c r="M39">
-        <v>4.5464342</v>
+        <v>4.6693108</v>
       </c>
       <c r="N39">
-        <v>16.9535658</v>
+        <v>16.8306892</v>
       </c>
       <c r="O39">
-        <v>5.001301911</v>
+        <v>4.965053314</v>
       </c>
       <c r="P39">
-        <v>11.952263889</v>
+        <v>11.865635886</v>
       </c>
       <c r="Q39">
-        <v>15.452263889</v>
+        <v>15.365635886</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1464329820456303</v>
+        <v>0.1477174793152219</v>
       </c>
       <c r="T39">
-        <v>1.556760227122441</v>
+        <v>1.576630991363938</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.72898079114397</v>
+        <v>4.604533928219128</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1063997071754376</v>
+        <v>0.106809005662128</v>
       </c>
       <c r="C40">
-        <v>169.9159077226996</v>
+        <v>166.2317074289227</v>
       </c>
       <c r="D40">
-        <v>217.9519077226996</v>
+        <v>216.4897074289227</v>
       </c>
       <c r="E40">
-        <v>83.23599999999999</v>
+        <v>85.458</v>
       </c>
       <c r="F40">
-        <v>84.43599999999999</v>
+        <v>86.658</v>
       </c>
       <c r="G40">
         <v>36.4</v>
@@ -4567,45 +4567,45 @@
         <v>21.5</v>
       </c>
       <c r="M40">
-        <v>4.6693108</v>
+        <v>5.0088324</v>
       </c>
       <c r="N40">
-        <v>16.8306892</v>
+        <v>16.4911676</v>
       </c>
       <c r="O40">
-        <v>4.965053314</v>
+        <v>4.864894442</v>
       </c>
       <c r="P40">
-        <v>11.865635886</v>
+        <v>11.626273158</v>
       </c>
       <c r="Q40">
-        <v>15.365635886</v>
+        <v>15.126273158</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1477174793152219</v>
+        <v>0.1490440912493902</v>
       </c>
       <c r="T40">
-        <v>1.576630991363938</v>
+        <v>1.59715325607237</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.295</v>
       </c>
       <c r="W40">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.604533928219128</v>
+        <v>4.292417530281109</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.106809005662128</v>
+        <v>0.1065485541488185</v>
       </c>
       <c r="C41">
-        <v>166.2317074289227</v>
+        <v>164.937878851368</v>
       </c>
       <c r="D41">
-        <v>216.4897074289227</v>
+        <v>217.417878851368</v>
       </c>
       <c r="E41">
-        <v>85.458</v>
+        <v>87.67999999999999</v>
       </c>
       <c r="F41">
-        <v>86.658</v>
+        <v>88.88</v>
       </c>
       <c r="G41">
         <v>36.4</v>
@@ -4649,28 +4649,28 @@
         <v>21.5</v>
       </c>
       <c r="M41">
-        <v>5.0088324</v>
+        <v>5.137264</v>
       </c>
       <c r="N41">
-        <v>16.4911676</v>
+        <v>16.362736</v>
       </c>
       <c r="O41">
-        <v>4.864894442</v>
+        <v>4.827007119999999</v>
       </c>
       <c r="P41">
-        <v>11.626273158</v>
+        <v>11.53572888</v>
       </c>
       <c r="Q41">
-        <v>15.126273158</v>
+        <v>15.03572888</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1490440912493902</v>
+        <v>0.1504149235813642</v>
       </c>
       <c r="T41">
-        <v>1.59715325607237</v>
+        <v>1.618359596271082</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.292417530281109</v>
+        <v>4.185107092024081</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1065485541488185</v>
+        <v>0.106288102635509</v>
       </c>
       <c r="C42">
-        <v>164.937878851368</v>
+        <v>163.6520433713334</v>
       </c>
       <c r="D42">
-        <v>217.417878851368</v>
+        <v>218.3540433713334</v>
       </c>
       <c r="E42">
-        <v>87.67999999999999</v>
+        <v>89.902</v>
       </c>
       <c r="F42">
-        <v>88.88</v>
+        <v>91.102</v>
       </c>
       <c r="G42">
         <v>36.4</v>
@@ -4731,28 +4731,28 @@
         <v>21.5</v>
       </c>
       <c r="M42">
-        <v>5.137264</v>
+        <v>5.265695600000001</v>
       </c>
       <c r="N42">
-        <v>16.362736</v>
+        <v>16.2343044</v>
       </c>
       <c r="O42">
-        <v>4.827007119999999</v>
+        <v>4.789119798</v>
       </c>
       <c r="P42">
-        <v>11.53572888</v>
+        <v>11.445184602</v>
       </c>
       <c r="Q42">
-        <v>15.03572888</v>
+        <v>14.945184602</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1504149235813642</v>
+        <v>0.1518322248059474</v>
       </c>
       <c r="T42">
-        <v>1.618359596271082</v>
+        <v>1.640284795459581</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.185107092024081</v>
+        <v>4.083031309291786</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.106288102635509</v>
+        <v>0.1070640011221994</v>
       </c>
       <c r="C43">
-        <v>163.6520433713334</v>
+        <v>158.6646253654702</v>
       </c>
       <c r="D43">
-        <v>218.3540433713334</v>
+        <v>215.5886253654701</v>
       </c>
       <c r="E43">
-        <v>89.902</v>
+        <v>92.124</v>
       </c>
       <c r="F43">
-        <v>91.102</v>
+        <v>93.324</v>
       </c>
       <c r="G43">
         <v>36.4</v>
@@ -4813,45 +4813,45 @@
         <v>21.5</v>
       </c>
       <c r="M43">
-        <v>5.265695600000001</v>
+        <v>5.7207612</v>
       </c>
       <c r="N43">
-        <v>16.2343044</v>
+        <v>15.7792388</v>
       </c>
       <c r="O43">
-        <v>4.789119798</v>
+        <v>4.654875446</v>
       </c>
       <c r="P43">
-        <v>11.445184602</v>
+        <v>11.124363354</v>
       </c>
       <c r="Q43">
-        <v>14.945184602</v>
+        <v>14.624363354</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1518322248059474</v>
+        <v>0.1532983984865507</v>
       </c>
       <c r="T43">
-        <v>1.640284795459581</v>
+        <v>1.662966035999407</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.295</v>
       </c>
       <c r="W43">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.083031309291786</v>
+        <v>3.758241123576352</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1070640011221994</v>
+        <v>0.1068282246088899</v>
       </c>
       <c r="C44">
-        <v>158.66462536547</v>
+        <v>157.2755307092455</v>
       </c>
       <c r="D44">
-        <v>215.58862536547</v>
+        <v>216.4215307092454</v>
       </c>
       <c r="E44">
-        <v>92.124</v>
+        <v>94.34599999999999</v>
       </c>
       <c r="F44">
-        <v>93.324</v>
+        <v>95.54599999999999</v>
       </c>
       <c r="G44">
         <v>36.4</v>
@@ -4895,28 +4895,28 @@
         <v>21.5</v>
       </c>
       <c r="M44">
-        <v>5.7207612</v>
+        <v>5.8569698</v>
       </c>
       <c r="N44">
-        <v>15.7792388</v>
+        <v>15.6430302</v>
       </c>
       <c r="O44">
-        <v>4.654875446</v>
+        <v>4.614693909</v>
       </c>
       <c r="P44">
-        <v>11.124363354</v>
+        <v>11.028336291</v>
       </c>
       <c r="Q44">
-        <v>14.624363354</v>
+        <v>14.528336291</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1532983984865507</v>
+        <v>0.1548160168577015</v>
       </c>
       <c r="T44">
-        <v>1.662966035999407</v>
+        <v>1.686443109540631</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.758241123576352</v>
+        <v>3.670840167214112</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1068282246088899</v>
+        <v>0.1065924480955803</v>
       </c>
       <c r="C45">
-        <v>157.2755307092455</v>
+        <v>155.8928967080536</v>
       </c>
       <c r="D45">
-        <v>216.4215307092454</v>
+        <v>217.2608967080536</v>
       </c>
       <c r="E45">
-        <v>94.34599999999999</v>
+        <v>96.568</v>
       </c>
       <c r="F45">
-        <v>95.54599999999999</v>
+        <v>97.768</v>
       </c>
       <c r="G45">
         <v>36.4</v>
@@ -4977,28 +4977,28 @@
         <v>21.5</v>
       </c>
       <c r="M45">
-        <v>5.8569698</v>
+        <v>5.9931784</v>
       </c>
       <c r="N45">
-        <v>15.6430302</v>
+        <v>15.5068216</v>
       </c>
       <c r="O45">
-        <v>4.614693909</v>
+        <v>4.574512372</v>
       </c>
       <c r="P45">
-        <v>11.028336291</v>
+        <v>10.932309228</v>
       </c>
       <c r="Q45">
-        <v>14.528336291</v>
+        <v>14.432309228</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1548160168577015</v>
+        <v>0.1563878358849649</v>
       </c>
       <c r="T45">
-        <v>1.686443109540631</v>
+        <v>1.710758649994042</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.670840167214112</v>
+        <v>3.587411981595609</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1065924480955803</v>
+        <v>0.1063566715822708</v>
       </c>
       <c r="C46">
-        <v>155.8928967080536</v>
+        <v>154.5167988252916</v>
       </c>
       <c r="D46">
-        <v>217.2608967080536</v>
+        <v>218.1067988252916</v>
       </c>
       <c r="E46">
-        <v>96.568</v>
+        <v>98.78999999999999</v>
       </c>
       <c r="F46">
-        <v>97.768</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="G46">
         <v>36.4</v>
@@ -5059,28 +5059,28 @@
         <v>21.5</v>
       </c>
       <c r="M46">
-        <v>5.9931784</v>
+        <v>6.129386999999999</v>
       </c>
       <c r="N46">
-        <v>15.5068216</v>
+        <v>15.370613</v>
       </c>
       <c r="O46">
-        <v>4.574512372</v>
+        <v>4.534330835</v>
       </c>
       <c r="P46">
-        <v>10.932309228</v>
+        <v>10.836282165</v>
       </c>
       <c r="Q46">
-        <v>14.432309228</v>
+        <v>14.336282165</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1563878358849649</v>
+        <v>0.1580168119677651</v>
       </c>
       <c r="T46">
-        <v>1.710758649994042</v>
+        <v>1.735958391918485</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.587411981595609</v>
+        <v>3.507691715337929</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1063566715822708</v>
+        <v>0.1070289350689613</v>
       </c>
       <c r="C47">
-        <v>154.5167988252916</v>
+        <v>149.9000938237422</v>
       </c>
       <c r="D47">
-        <v>218.1067988252916</v>
+        <v>215.7120938237422</v>
       </c>
       <c r="E47">
-        <v>98.78999999999999</v>
+        <v>101.012</v>
       </c>
       <c r="F47">
-        <v>99.98999999999999</v>
+        <v>102.212</v>
       </c>
       <c r="G47">
         <v>36.4</v>
@@ -5141,45 +5141,45 @@
         <v>21.5</v>
       </c>
       <c r="M47">
-        <v>6.129386999999999</v>
+        <v>6.551789200000001</v>
       </c>
       <c r="N47">
-        <v>15.370613</v>
+        <v>14.9482108</v>
       </c>
       <c r="O47">
-        <v>4.534330835</v>
+        <v>4.409722185999999</v>
       </c>
       <c r="P47">
-        <v>10.836282165</v>
+        <v>10.538488614</v>
       </c>
       <c r="Q47">
-        <v>14.336282165</v>
+        <v>14.038488614</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1580168119677651</v>
+        <v>0.1597061204980764</v>
       </c>
       <c r="T47">
-        <v>1.735958391918485</v>
+        <v>1.762091457617909</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.295</v>
       </c>
       <c r="W47">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.507691715337929</v>
+        <v>3.281546359885937</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1070289350689613</v>
+        <v>0.1068128985556517</v>
       </c>
       <c r="C48">
-        <v>149.9000938237422</v>
+        <v>148.441894425444</v>
       </c>
       <c r="D48">
-        <v>215.7120938237422</v>
+        <v>216.475894425444</v>
       </c>
       <c r="E48">
-        <v>101.012</v>
+        <v>103.234</v>
       </c>
       <c r="F48">
-        <v>102.212</v>
+        <v>104.434</v>
       </c>
       <c r="G48">
         <v>36.4</v>
@@ -5223,28 +5223,28 @@
         <v>21.5</v>
       </c>
       <c r="M48">
-        <v>6.551789200000001</v>
+        <v>6.694219400000001</v>
       </c>
       <c r="N48">
-        <v>14.9482108</v>
+        <v>14.8057806</v>
       </c>
       <c r="O48">
-        <v>4.409722185999999</v>
+        <v>4.367705277</v>
       </c>
       <c r="P48">
-        <v>10.538488614</v>
+        <v>10.438075323</v>
       </c>
       <c r="Q48">
-        <v>14.038488614</v>
+        <v>13.938075323</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1597061204980764</v>
+        <v>0.1614591765200976</v>
       </c>
       <c r="T48">
-        <v>1.762091457617909</v>
+        <v>1.789210676739951</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.281546359885937</v>
+        <v>3.211726224569215</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1068128985556517</v>
+        <v>0.1065968620423422</v>
       </c>
       <c r="C49">
-        <v>148.441894425444</v>
+        <v>146.9891232289745</v>
       </c>
       <c r="D49">
-        <v>216.475894425444</v>
+        <v>217.2451232289745</v>
       </c>
       <c r="E49">
-        <v>103.234</v>
+        <v>105.456</v>
       </c>
       <c r="F49">
-        <v>104.434</v>
+        <v>106.656</v>
       </c>
       <c r="G49">
         <v>36.4</v>
@@ -5305,28 +5305,28 @@
         <v>21.5</v>
       </c>
       <c r="M49">
-        <v>6.694219400000001</v>
+        <v>6.836649600000001</v>
       </c>
       <c r="N49">
-        <v>14.8057806</v>
+        <v>14.6633504</v>
       </c>
       <c r="O49">
-        <v>4.367705277</v>
+        <v>4.325688368</v>
       </c>
       <c r="P49">
-        <v>10.438075323</v>
+        <v>10.337662032</v>
       </c>
       <c r="Q49">
-        <v>13.938075323</v>
+        <v>13.837662032</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1614591765200976</v>
+        <v>0.163279657773735</v>
       </c>
       <c r="T49">
-        <v>1.789210676739951</v>
+        <v>1.817372942751303</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.211726224569215</v>
+        <v>3.144815261557357</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1065968620423422</v>
+        <v>0.1063808255290326</v>
       </c>
       <c r="C50">
-        <v>146.9891232289745</v>
+        <v>145.5418383066586</v>
       </c>
       <c r="D50">
-        <v>217.2451232289745</v>
+        <v>218.0198383066586</v>
       </c>
       <c r="E50">
-        <v>105.456</v>
+        <v>107.678</v>
       </c>
       <c r="F50">
-        <v>106.656</v>
+        <v>108.878</v>
       </c>
       <c r="G50">
         <v>36.4</v>
@@ -5387,28 +5387,28 @@
         <v>21.5</v>
       </c>
       <c r="M50">
-        <v>6.8366496</v>
+        <v>6.979079799999999</v>
       </c>
       <c r="N50">
-        <v>14.6633504</v>
+        <v>14.5209202</v>
       </c>
       <c r="O50">
-        <v>4.325688368</v>
+        <v>4.283671459</v>
       </c>
       <c r="P50">
-        <v>10.337662032</v>
+        <v>10.237248741</v>
       </c>
       <c r="Q50">
-        <v>13.837662032</v>
+        <v>13.737248741</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.163279657773735</v>
+        <v>0.1651715304490836</v>
       </c>
       <c r="T50">
-        <v>1.817372942751303</v>
+        <v>1.846639611351336</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.144815261557357</v>
+        <v>3.080635358260269</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1063808255290326</v>
+        <v>0.1061647890157231</v>
       </c>
       <c r="C51">
-        <v>145.5418383066586</v>
+        <v>144.1000985621498</v>
       </c>
       <c r="D51">
-        <v>218.0198383066586</v>
+        <v>218.8000985621498</v>
       </c>
       <c r="E51">
-        <v>107.678</v>
+        <v>109.9</v>
       </c>
       <c r="F51">
-        <v>108.878</v>
+        <v>111.1</v>
       </c>
       <c r="G51">
         <v>36.4</v>
@@ -5469,28 +5469,28 @@
         <v>21.5</v>
       </c>
       <c r="M51">
-        <v>6.979079799999999</v>
+        <v>7.12151</v>
       </c>
       <c r="N51">
-        <v>14.5209202</v>
+        <v>14.37849</v>
       </c>
       <c r="O51">
-        <v>4.283671459</v>
+        <v>4.24165455</v>
       </c>
       <c r="P51">
-        <v>10.237248741</v>
+        <v>10.13683545</v>
       </c>
       <c r="Q51">
-        <v>13.737248741</v>
+        <v>13.63683545</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1651715304490836</v>
+        <v>0.1671390780314462</v>
       </c>
       <c r="T51">
-        <v>1.846639611351336</v>
+        <v>1.87707694669537</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.080635358260269</v>
+        <v>3.019022651095063</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1061647890157231</v>
+        <v>0.1087532425024136</v>
       </c>
       <c r="C52">
-        <v>144.1000985621498</v>
+        <v>132.8816774804286</v>
       </c>
       <c r="D52">
-        <v>218.8000985621498</v>
+        <v>209.8036774804286</v>
       </c>
       <c r="E52">
-        <v>109.9</v>
+        <v>112.122</v>
       </c>
       <c r="F52">
-        <v>111.1</v>
+        <v>113.322</v>
       </c>
       <c r="G52">
         <v>36.4</v>
@@ -5551,45 +5551,45 @@
         <v>21.5</v>
       </c>
       <c r="M52">
-        <v>7.12151</v>
+        <v>8.147851800000002</v>
       </c>
       <c r="N52">
-        <v>14.37849</v>
+        <v>13.3521482</v>
       </c>
       <c r="O52">
-        <v>4.24165455</v>
+        <v>3.938883718999999</v>
       </c>
       <c r="P52">
-        <v>10.13683545</v>
+        <v>9.413264480999999</v>
       </c>
       <c r="Q52">
-        <v>13.63683545</v>
+        <v>12.913264481</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1671390780314462</v>
+        <v>0.169186933678395</v>
       </c>
       <c r="T52">
-        <v>1.87707694669537</v>
+        <v>1.908756622257528</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.295</v>
       </c>
       <c r="W52">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.019022651095063</v>
+        <v>2.638732334331363</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1087532425024136</v>
+        <v>0.108592195989104</v>
       </c>
       <c r="C53">
-        <v>132.8816774804286</v>
+        <v>131.1977722262089</v>
       </c>
       <c r="D53">
-        <v>209.8036774804286</v>
+        <v>210.3417722262089</v>
       </c>
       <c r="E53">
-        <v>112.122</v>
+        <v>114.344</v>
       </c>
       <c r="F53">
-        <v>113.322</v>
+        <v>115.544</v>
       </c>
       <c r="G53">
         <v>36.4</v>
@@ -5633,28 +5633,28 @@
         <v>21.5</v>
       </c>
       <c r="M53">
-        <v>8.147851800000002</v>
+        <v>8.3076136</v>
       </c>
       <c r="N53">
-        <v>13.3521482</v>
+        <v>13.1923864</v>
       </c>
       <c r="O53">
-        <v>3.938883718999999</v>
+        <v>3.891753988</v>
       </c>
       <c r="P53">
-        <v>9.413264480999999</v>
+        <v>9.300632412000001</v>
       </c>
       <c r="Q53">
-        <v>12.913264481</v>
+        <v>12.800632412</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.169186933678395</v>
+        <v>0.1713201166439667</v>
       </c>
       <c r="T53">
-        <v>1.908756622257528</v>
+        <v>1.941756284301442</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.638732334331363</v>
+        <v>2.587987481748068</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.108592195989104</v>
+        <v>0.1084311494757945</v>
       </c>
       <c r="C54">
-        <v>131.1977722262089</v>
+        <v>129.5166342302421</v>
       </c>
       <c r="D54">
-        <v>210.3417722262089</v>
+        <v>210.8826342302421</v>
       </c>
       <c r="E54">
-        <v>114.344</v>
+        <v>116.566</v>
       </c>
       <c r="F54">
-        <v>115.544</v>
+        <v>117.766</v>
       </c>
       <c r="G54">
         <v>36.4</v>
@@ -5715,28 +5715,28 @@
         <v>21.5</v>
       </c>
       <c r="M54">
-        <v>8.3076136</v>
+        <v>8.467375400000002</v>
       </c>
       <c r="N54">
-        <v>13.1923864</v>
+        <v>13.0326246</v>
       </c>
       <c r="O54">
-        <v>3.891753988</v>
+        <v>3.844624256999999</v>
       </c>
       <c r="P54">
-        <v>9.300632412000001</v>
+        <v>9.188000342999999</v>
       </c>
       <c r="Q54">
-        <v>12.800632412</v>
+        <v>12.688000343</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1713201166439667</v>
+        <v>0.1735440733527542</v>
       </c>
       <c r="T54">
-        <v>1.941756284301442</v>
+        <v>1.976160187283396</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.587987481748068</v>
+        <v>2.539157529262255</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1084311494757945</v>
+        <v>0.1097548329624849</v>
       </c>
       <c r="C55">
-        <v>129.5166342302421</v>
+        <v>122.9299623574519</v>
       </c>
       <c r="D55">
-        <v>210.8826342302421</v>
+        <v>206.5179623574519</v>
       </c>
       <c r="E55">
-        <v>116.566</v>
+        <v>118.788</v>
       </c>
       <c r="F55">
-        <v>117.766</v>
+        <v>119.988</v>
       </c>
       <c r="G55">
         <v>36.4</v>
@@ -5797,45 +5797,45 @@
         <v>21.5</v>
       </c>
       <c r="M55">
-        <v>8.467375400000002</v>
+        <v>9.0950904</v>
       </c>
       <c r="N55">
-        <v>13.0326246</v>
+        <v>12.4049096</v>
       </c>
       <c r="O55">
-        <v>3.844624256999999</v>
+        <v>3.659448332</v>
       </c>
       <c r="P55">
-        <v>9.188000342999999</v>
+        <v>8.745461268</v>
       </c>
       <c r="Q55">
-        <v>12.688000343</v>
+        <v>12.245461268</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1735440733527542</v>
+        <v>0.175864723831489</v>
       </c>
       <c r="T55">
-        <v>1.976160187283396</v>
+        <v>2.012059912134129</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.295</v>
       </c>
       <c r="W55">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.539157529262255</v>
+        <v>2.363912732522153</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1097548329624849</v>
+        <v>0.1096212814491754</v>
       </c>
       <c r="C56">
-        <v>122.9299623574519</v>
+        <v>121.1401189323775</v>
       </c>
       <c r="D56">
-        <v>206.5179623574519</v>
+        <v>206.9501189323775</v>
       </c>
       <c r="E56">
-        <v>118.788</v>
+        <v>121.01</v>
       </c>
       <c r="F56">
-        <v>119.988</v>
+        <v>122.21</v>
       </c>
       <c r="G56">
         <v>36.4</v>
@@ -5879,28 +5879,28 @@
         <v>21.5</v>
       </c>
       <c r="M56">
-        <v>9.0950904</v>
+        <v>9.263518000000001</v>
       </c>
       <c r="N56">
-        <v>12.4049096</v>
+        <v>12.236482</v>
       </c>
       <c r="O56">
-        <v>3.659448332</v>
+        <v>3.60976219</v>
       </c>
       <c r="P56">
-        <v>8.745461268</v>
+        <v>8.626719809999999</v>
       </c>
       <c r="Q56">
-        <v>12.245461268</v>
+        <v>12.12671981</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.175864723831489</v>
+        <v>0.1782885143315009</v>
       </c>
       <c r="T56">
-        <v>2.012059912134129</v>
+        <v>2.049555180311563</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.363912732522153</v>
+        <v>2.320932501021749</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1096212814491754</v>
+        <v>0.1094877299358659</v>
       </c>
       <c r="C57">
-        <v>121.1401189323775</v>
+        <v>119.3520879494997</v>
       </c>
       <c r="D57">
-        <v>206.9501189323775</v>
+        <v>207.3840879494997</v>
       </c>
       <c r="E57">
-        <v>121.01</v>
+        <v>123.232</v>
       </c>
       <c r="F57">
-        <v>122.21</v>
+        <v>124.432</v>
       </c>
       <c r="G57">
         <v>36.4</v>
@@ -5961,28 +5961,28 @@
         <v>21.5</v>
       </c>
       <c r="M57">
-        <v>9.263518000000001</v>
+        <v>9.431945600000001</v>
       </c>
       <c r="N57">
-        <v>12.236482</v>
+        <v>12.0680544</v>
       </c>
       <c r="O57">
-        <v>3.60976219</v>
+        <v>3.560076048</v>
       </c>
       <c r="P57">
-        <v>8.626719809999999</v>
+        <v>8.507978352</v>
       </c>
       <c r="Q57">
-        <v>12.12671981</v>
+        <v>12.007978352</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1782885143315009</v>
+        <v>0.1808224771269679</v>
       </c>
       <c r="T57">
-        <v>2.049555180311563</v>
+        <v>2.088754778860697</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.320932501021749</v>
+        <v>2.279487277789219</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1094877299358659</v>
+        <v>0.1093541784225563</v>
       </c>
       <c r="C58">
-        <v>119.3520879494997</v>
+        <v>117.5658808347106</v>
       </c>
       <c r="D58">
-        <v>207.3840879494997</v>
+        <v>207.8198808347106</v>
       </c>
       <c r="E58">
-        <v>123.232</v>
+        <v>125.454</v>
       </c>
       <c r="F58">
-        <v>124.432</v>
+        <v>126.654</v>
       </c>
       <c r="G58">
         <v>36.4</v>
@@ -6043,28 +6043,28 @@
         <v>21.5</v>
       </c>
       <c r="M58">
-        <v>9.431945600000001</v>
+        <v>9.600373200000002</v>
       </c>
       <c r="N58">
-        <v>12.0680544</v>
+        <v>11.8996268</v>
       </c>
       <c r="O58">
-        <v>3.560076048</v>
+        <v>3.510389905999999</v>
       </c>
       <c r="P58">
-        <v>8.507978352</v>
+        <v>8.389236894</v>
       </c>
       <c r="Q58">
-        <v>12.007978352</v>
+        <v>11.889236894</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1808224771269679</v>
+        <v>0.1834742986571077</v>
       </c>
       <c r="T58">
-        <v>2.088754778860697</v>
+        <v>2.129777614551652</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.279487277789219</v>
+        <v>2.239496272915723</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1093541784225563</v>
+        <v>0.1092206269092468</v>
       </c>
       <c r="C59">
-        <v>117.5658808347106</v>
+        <v>115.7815091101454</v>
       </c>
       <c r="D59">
-        <v>207.8198808347106</v>
+        <v>208.2575091101453</v>
       </c>
       <c r="E59">
-        <v>125.454</v>
+        <v>127.676</v>
       </c>
       <c r="F59">
-        <v>126.654</v>
+        <v>128.876</v>
       </c>
       <c r="G59">
         <v>36.4</v>
@@ -6125,28 +6125,28 @@
         <v>21.5</v>
       </c>
       <c r="M59">
-        <v>9.600373200000002</v>
+        <v>9.768800800000001</v>
       </c>
       <c r="N59">
-        <v>11.8996268</v>
+        <v>11.7311992</v>
       </c>
       <c r="O59">
-        <v>3.510389905999999</v>
+        <v>3.460703763999999</v>
       </c>
       <c r="P59">
-        <v>8.389236894</v>
+        <v>8.270495435999999</v>
       </c>
       <c r="Q59">
-        <v>11.889236894</v>
+        <v>11.770495436</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1834742986571077</v>
+        <v>0.1862523974029685</v>
       </c>
       <c r="T59">
-        <v>2.129777614551652</v>
+        <v>2.172753918608843</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.239496272915723</v>
+        <v>2.20088426821028</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1092206269092468</v>
+        <v>0.1090870753959372</v>
       </c>
       <c r="C60">
-        <v>115.7815091101454</v>
+        <v>113.9989843951973</v>
       </c>
       <c r="D60">
-        <v>208.2575091101453</v>
+        <v>208.6969843951973</v>
       </c>
       <c r="E60">
-        <v>127.676</v>
+        <v>129.898</v>
       </c>
       <c r="F60">
-        <v>128.876</v>
+        <v>131.098</v>
       </c>
       <c r="G60">
         <v>36.4</v>
@@ -6207,28 +6207,28 @@
         <v>21.5</v>
       </c>
       <c r="M60">
-        <v>9.768800799999999</v>
+        <v>9.9372284</v>
       </c>
       <c r="N60">
-        <v>11.7311992</v>
+        <v>11.5627716</v>
       </c>
       <c r="O60">
-        <v>3.460703764</v>
+        <v>3.411017622</v>
       </c>
       <c r="P60">
-        <v>8.270495436000001</v>
+        <v>8.151753978</v>
       </c>
       <c r="Q60">
-        <v>11.770495436</v>
+        <v>11.651753978</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1862523974029685</v>
+        <v>0.1891660131608225</v>
       </c>
       <c r="T60">
-        <v>2.172753918608842</v>
+        <v>2.217826627741994</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.20088426821028</v>
+        <v>2.163581145020276</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1090870753959372</v>
+        <v>0.1089535238826277</v>
       </c>
       <c r="C61">
-        <v>113.9989843951973</v>
+        <v>112.2183184075466</v>
       </c>
       <c r="D61">
-        <v>208.6969843951973</v>
+        <v>209.1383184075466</v>
       </c>
       <c r="E61">
-        <v>129.898</v>
+        <v>132.12</v>
       </c>
       <c r="F61">
-        <v>131.098</v>
+        <v>133.32</v>
       </c>
       <c r="G61">
         <v>36.4</v>
@@ -6289,28 +6289,28 @@
         <v>21.5</v>
       </c>
       <c r="M61">
-        <v>9.9372284</v>
+        <v>10.105656</v>
       </c>
       <c r="N61">
-        <v>11.5627716</v>
+        <v>11.394344</v>
       </c>
       <c r="O61">
-        <v>3.411017622</v>
+        <v>3.36133148</v>
       </c>
       <c r="P61">
-        <v>8.151753978</v>
+        <v>8.03301252</v>
       </c>
       <c r="Q61">
-        <v>11.651753978</v>
+        <v>11.53301252</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1891660131608225</v>
+        <v>0.1922253097065692</v>
       </c>
       <c r="T61">
-        <v>2.217826627741994</v>
+        <v>2.265152972331803</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.163581145020276</v>
+        <v>2.127521459269937</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1089535238826277</v>
+        <v>0.1088199723693182</v>
       </c>
       <c r="C62">
-        <v>112.2183184075466</v>
+        <v>110.4395229642014</v>
       </c>
       <c r="D62">
-        <v>209.1383184075466</v>
+        <v>209.5815229642014</v>
       </c>
       <c r="E62">
-        <v>132.12</v>
+        <v>134.342</v>
       </c>
       <c r="F62">
-        <v>133.32</v>
+        <v>135.542</v>
       </c>
       <c r="G62">
         <v>36.4</v>
@@ -6371,28 +6371,28 @@
         <v>21.5</v>
       </c>
       <c r="M62">
-        <v>10.105656</v>
+        <v>10.2740836</v>
       </c>
       <c r="N62">
-        <v>11.394344</v>
+        <v>11.2259164</v>
       </c>
       <c r="O62">
-        <v>3.36133148</v>
+        <v>3.311645337999999</v>
       </c>
       <c r="P62">
-        <v>8.03301252</v>
+        <v>7.914271061999999</v>
       </c>
       <c r="Q62">
-        <v>11.53301252</v>
+        <v>11.414271062</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1922253097065692</v>
+        <v>0.1954414932546619</v>
       </c>
       <c r="T62">
-        <v>2.265152972331803</v>
+        <v>2.314906308951858</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.127521459269937</v>
+        <v>2.092644058298299</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1088199723693182</v>
+        <v>0.1086864208560086</v>
       </c>
       <c r="C63">
-        <v>110.4395229642014</v>
+        <v>108.6626099825527</v>
       </c>
       <c r="D63">
-        <v>209.5815229642014</v>
+        <v>210.0266099825526</v>
       </c>
       <c r="E63">
-        <v>134.342</v>
+        <v>136.564</v>
       </c>
       <c r="F63">
-        <v>135.542</v>
+        <v>137.764</v>
       </c>
       <c r="G63">
         <v>36.4</v>
@@ -6453,28 +6453,28 @@
         <v>21.5</v>
       </c>
       <c r="M63">
-        <v>10.2740836</v>
+        <v>10.4425112</v>
       </c>
       <c r="N63">
-        <v>11.2259164</v>
+        <v>11.0574888</v>
       </c>
       <c r="O63">
-        <v>3.311645337999999</v>
+        <v>3.261959196</v>
       </c>
       <c r="P63">
-        <v>7.914271061999999</v>
+        <v>7.795529604</v>
       </c>
       <c r="Q63">
-        <v>11.414271062</v>
+        <v>11.295529604</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1954414932546619</v>
+        <v>0.1988269496210753</v>
       </c>
       <c r="T63">
-        <v>2.314906308951858</v>
+        <v>2.367278242236127</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.092644058298299</v>
+        <v>2.058891734777359</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1086864208560086</v>
+        <v>0.1085528693426991</v>
       </c>
       <c r="C64">
-        <v>108.6626099825527</v>
+        <v>106.8875914814426</v>
       </c>
       <c r="D64">
-        <v>210.0266099825526</v>
+        <v>210.4735914814426</v>
       </c>
       <c r="E64">
-        <v>136.564</v>
+        <v>138.786</v>
       </c>
       <c r="F64">
-        <v>137.764</v>
+        <v>139.986</v>
       </c>
       <c r="G64">
         <v>36.4</v>
@@ -6535,28 +6535,28 @@
         <v>21.5</v>
       </c>
       <c r="M64">
-        <v>10.4425112</v>
+        <v>10.6109388</v>
       </c>
       <c r="N64">
-        <v>11.0574888</v>
+        <v>10.8890612</v>
       </c>
       <c r="O64">
-        <v>3.261959196</v>
+        <v>3.212273054</v>
       </c>
       <c r="P64">
-        <v>7.795529604</v>
+        <v>7.676788146000001</v>
       </c>
       <c r="Q64">
-        <v>11.295529604</v>
+        <v>11.176788146</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1988269496210753</v>
+        <v>0.2023954036289164</v>
       </c>
       <c r="T64">
-        <v>2.367278242236127</v>
+        <v>2.422481090833059</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.058891734777359</v>
+        <v>2.026210913590416</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1085528693426991</v>
+        <v>0.1148263578293895</v>
       </c>
       <c r="C65">
-        <v>106.8875914814426</v>
+        <v>85.5366138787879</v>
       </c>
       <c r="D65">
-        <v>210.4735914814426</v>
+        <v>191.3446138787879</v>
       </c>
       <c r="E65">
-        <v>138.786</v>
+        <v>141.008</v>
       </c>
       <c r="F65">
-        <v>139.986</v>
+        <v>142.208</v>
       </c>
       <c r="G65">
         <v>36.4</v>
@@ -6617,45 +6617,45 @@
         <v>21.5</v>
       </c>
       <c r="M65">
-        <v>10.6109388</v>
+        <v>12.79872</v>
       </c>
       <c r="N65">
-        <v>10.8890612</v>
+        <v>8.701280000000001</v>
       </c>
       <c r="O65">
-        <v>3.212273054</v>
+        <v>2.5668776</v>
       </c>
       <c r="P65">
-        <v>7.676788146000001</v>
+        <v>6.134402400000001</v>
       </c>
       <c r="Q65">
-        <v>11.176788146</v>
+        <v>9.634402400000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2023954036289164</v>
+        <v>0.2061621050816376</v>
       </c>
       <c r="T65">
-        <v>2.422481090833059</v>
+        <v>2.480750764352044</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.295</v>
       </c>
       <c r="W65">
-        <v>0.05343900000000001</v>
+        <v>0.06345000000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.026210913590416</v>
+        <v>1.679855485548555</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1148263578293895</v>
+        <v>0.11479291631608</v>
       </c>
       <c r="C66">
-        <v>85.5366138787879</v>
+        <v>83.40736040688677</v>
       </c>
       <c r="D66">
-        <v>191.3446138787879</v>
+        <v>191.4373604068868</v>
       </c>
       <c r="E66">
-        <v>141.008</v>
+        <v>143.23</v>
       </c>
       <c r="F66">
-        <v>142.208</v>
+        <v>144.43</v>
       </c>
       <c r="G66">
         <v>36.4</v>
@@ -6699,28 +6699,28 @@
         <v>21.5</v>
       </c>
       <c r="M66">
-        <v>12.79872</v>
+        <v>12.9987</v>
       </c>
       <c r="N66">
-        <v>8.701280000000001</v>
+        <v>8.501300000000001</v>
       </c>
       <c r="O66">
-        <v>2.5668776</v>
+        <v>2.5078835</v>
       </c>
       <c r="P66">
-        <v>6.134402400000001</v>
+        <v>5.9934165</v>
       </c>
       <c r="Q66">
-        <v>9.634402400000001</v>
+        <v>9.4934165</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2061621050816376</v>
+        <v>0.2101440466173714</v>
       </c>
       <c r="T66">
-        <v>2.480750764352044</v>
+        <v>2.542350133500684</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.679855485548555</v>
+        <v>1.654011555001654</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.11479291631608</v>
+        <v>0.1147594748027705</v>
       </c>
       <c r="C67">
-        <v>83.40736040688677</v>
+        <v>81.27819688881047</v>
       </c>
       <c r="D67">
-        <v>191.4373604068868</v>
+        <v>191.5301968888105</v>
       </c>
       <c r="E67">
-        <v>143.23</v>
+        <v>145.452</v>
       </c>
       <c r="F67">
-        <v>144.43</v>
+        <v>146.652</v>
       </c>
       <c r="G67">
         <v>36.4</v>
@@ -6781,28 +6781,28 @@
         <v>21.5</v>
       </c>
       <c r="M67">
-        <v>12.9987</v>
+        <v>13.19868</v>
       </c>
       <c r="N67">
-        <v>8.501300000000001</v>
+        <v>8.301320000000002</v>
       </c>
       <c r="O67">
-        <v>2.5078835</v>
+        <v>2.448889400000001</v>
       </c>
       <c r="P67">
-        <v>5.9934165</v>
+        <v>5.852430600000002</v>
       </c>
       <c r="Q67">
-        <v>9.4934165</v>
+        <v>9.352430600000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2101440466173714</v>
+        <v>0.2143602200081484</v>
       </c>
       <c r="T67">
-        <v>2.542350133500684</v>
+        <v>2.607572994952185</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.654011555001654</v>
+        <v>1.628950773865266</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1147594748027705</v>
+        <v>0.1147260332894609</v>
       </c>
       <c r="C68">
-        <v>81.27819688881047</v>
+        <v>79.14912345549016</v>
       </c>
       <c r="D68">
-        <v>191.5301968888105</v>
+        <v>191.6231234554901</v>
       </c>
       <c r="E68">
-        <v>145.452</v>
+        <v>147.674</v>
       </c>
       <c r="F68">
-        <v>146.652</v>
+        <v>148.874</v>
       </c>
       <c r="G68">
         <v>36.4</v>
@@ -6863,28 +6863,28 @@
         <v>21.5</v>
       </c>
       <c r="M68">
-        <v>13.19868</v>
+        <v>13.39866</v>
       </c>
       <c r="N68">
-        <v>8.301320000000002</v>
+        <v>8.10134</v>
       </c>
       <c r="O68">
-        <v>2.448889400000001</v>
+        <v>2.3898953</v>
       </c>
       <c r="P68">
-        <v>5.852430600000002</v>
+        <v>5.7114447</v>
       </c>
       <c r="Q68">
-        <v>9.352430600000002</v>
+        <v>9.211444700000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2143602200081484</v>
+        <v>0.2188319190589725</v>
       </c>
       <c r="T68">
-        <v>2.607572994952185</v>
+        <v>2.676748757097716</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.628950773865266</v>
+        <v>1.604638075747873</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1147260332894609</v>
+        <v>0.1146925917761514</v>
       </c>
       <c r="C69">
-        <v>79.14912345549016</v>
+        <v>77.02014023811131</v>
       </c>
       <c r="D69">
-        <v>191.6231234554901</v>
+        <v>191.7161402381113</v>
       </c>
       <c r="E69">
-        <v>147.674</v>
+        <v>149.896</v>
       </c>
       <c r="F69">
-        <v>148.874</v>
+        <v>151.096</v>
       </c>
       <c r="G69">
         <v>36.4</v>
@@ -6945,28 +6945,28 @@
         <v>21.5</v>
       </c>
       <c r="M69">
-        <v>13.39866</v>
+        <v>13.59864</v>
       </c>
       <c r="N69">
-        <v>8.10134</v>
+        <v>7.90136</v>
       </c>
       <c r="O69">
-        <v>2.3898953</v>
+        <v>2.3309012</v>
       </c>
       <c r="P69">
-        <v>5.7114447</v>
+        <v>5.570458800000001</v>
       </c>
       <c r="Q69">
-        <v>9.211444700000001</v>
+        <v>9.070458800000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2188319190589725</v>
+        <v>0.223583099300473</v>
       </c>
       <c r="T69">
-        <v>2.676748757097716</v>
+        <v>2.750248004377344</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.604638075747873</v>
+        <v>1.581040456986875</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1146925917761514</v>
+        <v>0.1146591502628418</v>
       </c>
       <c r="C70">
-        <v>77.02014023811131</v>
+        <v>74.89124736811442</v>
       </c>
       <c r="D70">
-        <v>191.7161402381113</v>
+        <v>191.8092473681144</v>
       </c>
       <c r="E70">
-        <v>149.896</v>
+        <v>152.118</v>
       </c>
       <c r="F70">
-        <v>151.096</v>
+        <v>153.318</v>
       </c>
       <c r="G70">
         <v>36.4</v>
@@ -7027,28 +7027,28 @@
         <v>21.5</v>
       </c>
       <c r="M70">
-        <v>13.59864</v>
+        <v>13.79862</v>
       </c>
       <c r="N70">
-        <v>7.90136</v>
+        <v>7.701379999999999</v>
       </c>
       <c r="O70">
-        <v>2.3309012</v>
+        <v>2.2719071</v>
       </c>
       <c r="P70">
-        <v>5.570458800000001</v>
+        <v>5.429472899999999</v>
       </c>
       <c r="Q70">
-        <v>9.070458800000001</v>
+        <v>8.929472899999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.223583099300473</v>
+        <v>0.2286408072994898</v>
       </c>
       <c r="T70">
-        <v>2.750248004377344</v>
+        <v>2.828489138578238</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.581040456986875</v>
+        <v>1.558126827175471</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1146591502628418</v>
+        <v>0.1146257087495323</v>
       </c>
       <c r="C71">
-        <v>74.89124736811442</v>
+        <v>72.76244497719532</v>
       </c>
       <c r="D71">
-        <v>191.8092473681144</v>
+        <v>191.9024449771953</v>
       </c>
       <c r="E71">
-        <v>152.118</v>
+        <v>154.34</v>
       </c>
       <c r="F71">
-        <v>153.318</v>
+        <v>155.54</v>
       </c>
       <c r="G71">
         <v>36.4</v>
@@ -7109,28 +7109,28 @@
         <v>21.5</v>
       </c>
       <c r="M71">
-        <v>13.79862</v>
+        <v>13.9986</v>
       </c>
       <c r="N71">
-        <v>7.701379999999999</v>
+        <v>7.501399999999999</v>
       </c>
       <c r="O71">
-        <v>2.2719071</v>
+        <v>2.212912999999999</v>
       </c>
       <c r="P71">
-        <v>5.429472899999999</v>
+        <v>5.288486999999999</v>
       </c>
       <c r="Q71">
-        <v>8.929472899999999</v>
+        <v>8.788487</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2286408072994898</v>
+        <v>0.2340356958317743</v>
       </c>
       <c r="T71">
-        <v>2.828489138578238</v>
+        <v>2.911946348392525</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.558126827175471</v>
+        <v>1.535867872501536</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1146257087495323</v>
+        <v>0.1145922672362227</v>
       </c>
       <c r="C72">
-        <v>72.76244497719532</v>
+        <v>70.6337331973059</v>
       </c>
       <c r="D72">
-        <v>191.9024449771953</v>
+        <v>191.9957331973059</v>
       </c>
       <c r="E72">
-        <v>154.34</v>
+        <v>156.562</v>
       </c>
       <c r="F72">
-        <v>155.54</v>
+        <v>157.762</v>
       </c>
       <c r="G72">
         <v>36.4</v>
@@ -7191,28 +7191,28 @@
         <v>21.5</v>
       </c>
       <c r="M72">
-        <v>13.9986</v>
+        <v>14.19858</v>
       </c>
       <c r="N72">
-        <v>7.501399999999999</v>
+        <v>7.30142</v>
       </c>
       <c r="O72">
-        <v>2.212912999999999</v>
+        <v>2.1539189</v>
       </c>
       <c r="P72">
-        <v>5.288486999999999</v>
+        <v>5.1475011</v>
       </c>
       <c r="Q72">
-        <v>8.788487</v>
+        <v>8.647501099999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2340356958317743</v>
+        <v>0.2398026456421475</v>
       </c>
       <c r="T72">
-        <v>2.911946348392525</v>
+        <v>3.001159227849176</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.535867872501536</v>
+        <v>1.514235930635317</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1145922672362228</v>
+        <v>0.1473047222598748</v>
       </c>
       <c r="C73">
-        <v>70.63373319730587</v>
+        <v>6.536269207856236</v>
       </c>
       <c r="D73">
-        <v>191.9957331973058</v>
+        <v>130.1202692078562</v>
       </c>
       <c r="E73">
-        <v>156.562</v>
+        <v>158.784</v>
       </c>
       <c r="F73">
-        <v>157.762</v>
+        <v>159.984</v>
       </c>
       <c r="G73">
         <v>36.4</v>
@@ -7273,45 +7273,45 @@
         <v>21.5</v>
       </c>
       <c r="M73">
-        <v>14.19858</v>
+        <v>23.4856512</v>
       </c>
       <c r="N73">
-        <v>7.301420000000004</v>
+        <v>-1.9856512</v>
       </c>
       <c r="O73">
-        <v>2.153918900000001</v>
+        <v>-0.5857671039999999</v>
       </c>
       <c r="P73">
-        <v>5.147501100000003</v>
+        <v>-1.399884096</v>
       </c>
       <c r="Q73">
-        <v>8.647501100000003</v>
+        <v>2.100115904</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2398026456421474</v>
+        <v>0.2505458095368425</v>
       </c>
       <c r="T73">
-        <v>3.001159227849175</v>
+        <v>3.167352556564563</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.295</v>
+        <v>0.2700585113007213</v>
       </c>
       <c r="W73">
-        <v>0.06345000000000001</v>
+        <v>0.1071554105410541</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.514235930635317</v>
+        <v>0.9154525806804114</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1473047222598748</v>
+        <v>0.1483147222598749</v>
       </c>
       <c r="C74">
-        <v>6.536269207856236</v>
+        <v>3.032292639000246</v>
       </c>
       <c r="D74">
-        <v>130.1202692078562</v>
+        <v>128.8382926390002</v>
       </c>
       <c r="E74">
-        <v>158.784</v>
+        <v>161.006</v>
       </c>
       <c r="F74">
-        <v>159.984</v>
+        <v>162.206</v>
       </c>
       <c r="G74">
         <v>36.4</v>
@@ -7355,37 +7355,37 @@
         <v>21.5</v>
       </c>
       <c r="M74">
-        <v>23.4856512</v>
+        <v>23.8118408</v>
       </c>
       <c r="N74">
-        <v>-1.9856512</v>
+        <v>-2.311840800000002</v>
       </c>
       <c r="O74">
-        <v>-0.5857671039999999</v>
+        <v>-0.6819930360000006</v>
       </c>
       <c r="P74">
-        <v>-1.399884096</v>
+        <v>-1.629847764000002</v>
       </c>
       <c r="Q74">
-        <v>2.100115904</v>
+        <v>1.870152235999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2505458095368425</v>
+        <v>0.2581289876678366</v>
       </c>
       <c r="T74">
-        <v>3.167352556564563</v>
+        <v>3.284661910511398</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2700585113007213</v>
+        <v>0.2663590796390676</v>
       </c>
       <c r="W74">
-        <v>0.1071554105410541</v>
+        <v>0.1076984871089849</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9154525806804114</v>
+        <v>0.9029121343697207</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1483147222598749</v>
+        <v>0.1493247222598749</v>
       </c>
       <c r="C75">
-        <v>3.032292639000246</v>
+        <v>-0.4466696857934096</v>
       </c>
       <c r="D75">
-        <v>128.8382926390002</v>
+        <v>127.5813303142066</v>
       </c>
       <c r="E75">
-        <v>161.006</v>
+        <v>163.228</v>
       </c>
       <c r="F75">
-        <v>162.206</v>
+        <v>164.428</v>
       </c>
       <c r="G75">
         <v>36.4</v>
@@ -7437,37 +7437,37 @@
         <v>21.5</v>
       </c>
       <c r="M75">
-        <v>23.8118408</v>
+        <v>24.1380304</v>
       </c>
       <c r="N75">
-        <v>-2.311840800000002</v>
+        <v>-2.638030400000002</v>
       </c>
       <c r="O75">
-        <v>-0.6819930360000006</v>
+        <v>-0.7782189680000005</v>
       </c>
       <c r="P75">
-        <v>-1.629847764000002</v>
+        <v>-1.859811432000001</v>
       </c>
       <c r="Q75">
-        <v>1.870152235999998</v>
+        <v>1.640188567999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2581289876678366</v>
+        <v>0.2662954871935226</v>
       </c>
       <c r="T75">
-        <v>3.284661910511398</v>
+        <v>3.410995060915683</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2663590796390676</v>
+        <v>0.262759632616918</v>
       </c>
       <c r="W75">
-        <v>0.1076984871089849</v>
+        <v>0.1082268859318364</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9029121343697207</v>
+        <v>0.8907106190404002</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1493247222598749</v>
+        <v>0.1503347222598748</v>
       </c>
       <c r="C76">
-        <v>-0.4466696857934096</v>
+        <v>-3.901342819003702</v>
       </c>
       <c r="D76">
-        <v>127.5813303142066</v>
+        <v>126.3486571809963</v>
       </c>
       <c r="E76">
-        <v>163.228</v>
+        <v>165.45</v>
       </c>
       <c r="F76">
-        <v>164.428</v>
+        <v>166.65</v>
       </c>
       <c r="G76">
         <v>36.4</v>
@@ -7519,37 +7519,37 @@
         <v>21.5</v>
       </c>
       <c r="M76">
-        <v>24.1380304</v>
+        <v>24.46422</v>
       </c>
       <c r="N76">
-        <v>-2.638030400000002</v>
+        <v>-2.964219999999997</v>
       </c>
       <c r="O76">
-        <v>-0.7782189680000005</v>
+        <v>-0.8744448999999992</v>
       </c>
       <c r="P76">
-        <v>-1.859811432000001</v>
+        <v>-2.089775099999998</v>
       </c>
       <c r="Q76">
-        <v>1.640188567999999</v>
+        <v>1.410224900000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2662954871935226</v>
+        <v>0.2751153066812635</v>
       </c>
       <c r="T76">
-        <v>3.410995060915683</v>
+        <v>3.54743486335231</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.262759632616918</v>
+        <v>0.2592561708486925</v>
       </c>
       <c r="W76">
-        <v>0.1082268859318364</v>
+        <v>0.108741194119412</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8907106190404002</v>
+        <v>0.878834477453195</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1503347222598748</v>
+        <v>0.1513447222598749</v>
       </c>
       <c r="C77">
-        <v>-3.901342819003702</v>
+        <v>-7.332424059831624</v>
       </c>
       <c r="D77">
-        <v>126.3486571809963</v>
+        <v>125.1395759401684</v>
       </c>
       <c r="E77">
-        <v>165.45</v>
+        <v>167.672</v>
       </c>
       <c r="F77">
-        <v>166.65</v>
+        <v>168.872</v>
       </c>
       <c r="G77">
         <v>36.4</v>
@@ -7601,37 +7601,37 @@
         <v>21.5</v>
       </c>
       <c r="M77">
-        <v>24.46422</v>
+        <v>24.7904096</v>
       </c>
       <c r="N77">
-        <v>-2.964219999999997</v>
+        <v>-3.2904096</v>
       </c>
       <c r="O77">
-        <v>-0.8744448999999992</v>
+        <v>-0.970670832</v>
       </c>
       <c r="P77">
-        <v>-2.089775099999998</v>
+        <v>-2.319738768</v>
       </c>
       <c r="Q77">
-        <v>1.410224900000002</v>
+        <v>1.180261232</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2751153066812635</v>
+        <v>0.2846701111263162</v>
       </c>
       <c r="T77">
-        <v>3.54743486335231</v>
+        <v>3.695244649325323</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2592561708486925</v>
+        <v>0.2558449054427887</v>
       </c>
       <c r="W77">
-        <v>0.108741194119412</v>
+        <v>0.1092419678809986</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.878834477453195</v>
+        <v>0.8672708659077581</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1513447222598749</v>
+        <v>0.1523547222598749</v>
       </c>
       <c r="C78">
-        <v>-7.332424059831624</v>
+        <v>-10.74058426952479</v>
       </c>
       <c r="D78">
-        <v>125.1395759401684</v>
+        <v>123.9534157304752</v>
       </c>
       <c r="E78">
-        <v>167.672</v>
+        <v>169.894</v>
       </c>
       <c r="F78">
-        <v>168.872</v>
+        <v>171.094</v>
       </c>
       <c r="G78">
         <v>36.4</v>
@@ -7683,37 +7683,37 @@
         <v>21.5</v>
       </c>
       <c r="M78">
-        <v>24.7904096</v>
+        <v>25.1165992</v>
       </c>
       <c r="N78">
-        <v>-3.2904096</v>
+        <v>-3.616599200000003</v>
       </c>
       <c r="O78">
-        <v>-0.970670832</v>
+        <v>-1.066896764000001</v>
       </c>
       <c r="P78">
-        <v>-2.319738768</v>
+        <v>-2.549702436000002</v>
       </c>
       <c r="Q78">
-        <v>1.180261232</v>
+        <v>0.9502975639999978</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2846701111263162</v>
+        <v>0.2950557681318083</v>
       </c>
       <c r="T78">
-        <v>3.695244649325323</v>
+        <v>3.855907460165555</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2558449054427887</v>
+        <v>0.252522244333142</v>
       </c>
       <c r="W78">
-        <v>0.1092419678809986</v>
+        <v>0.1097297345318948</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8672708659077581</v>
+        <v>0.856007607908956</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1523547222598749</v>
+        <v>0.1533647222598749</v>
       </c>
       <c r="C79">
-        <v>-10.74058426952479</v>
+        <v>-14.12646911259924</v>
       </c>
       <c r="D79">
-        <v>123.9534157304752</v>
+        <v>122.7895308874008</v>
       </c>
       <c r="E79">
-        <v>169.894</v>
+        <v>172.116</v>
       </c>
       <c r="F79">
-        <v>171.094</v>
+        <v>173.316</v>
       </c>
       <c r="G79">
         <v>36.4</v>
@@ -7765,37 +7765,37 @@
         <v>21.5</v>
       </c>
       <c r="M79">
-        <v>25.1165992</v>
+        <v>25.4427888</v>
       </c>
       <c r="N79">
-        <v>-3.616599200000003</v>
+        <v>-3.942788800000002</v>
       </c>
       <c r="O79">
-        <v>-1.066896764000001</v>
+        <v>-1.163122696000001</v>
       </c>
       <c r="P79">
-        <v>-2.549702436000002</v>
+        <v>-2.779666104000002</v>
       </c>
       <c r="Q79">
-        <v>0.9502975639999978</v>
+        <v>0.7203338959999983</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2950557681318083</v>
+        <v>0.3063855757741632</v>
       </c>
       <c r="T79">
-        <v>3.855907460165555</v>
+        <v>4.031175981082171</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.252522244333142</v>
+        <v>0.2492847796622043</v>
       </c>
       <c r="W79">
-        <v>0.1097297345318948</v>
+        <v>0.1102049943455884</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.856007607908956</v>
+        <v>0.8450331513973027</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1533647222598749</v>
+        <v>0.1543747222598749</v>
       </c>
       <c r="C80">
-        <v>-14.12646911259924</v>
+        <v>-17.49070022878334</v>
       </c>
       <c r="D80">
-        <v>122.7895308874008</v>
+        <v>121.6472997712167</v>
       </c>
       <c r="E80">
-        <v>172.116</v>
+        <v>174.338</v>
       </c>
       <c r="F80">
-        <v>173.316</v>
+        <v>175.538</v>
       </c>
       <c r="G80">
         <v>36.4</v>
@@ -7847,37 +7847,37 @@
         <v>21.5</v>
       </c>
       <c r="M80">
-        <v>25.4427888</v>
+        <v>25.76897840000001</v>
       </c>
       <c r="N80">
-        <v>-3.942788800000002</v>
+        <v>-4.268978400000005</v>
       </c>
       <c r="O80">
-        <v>-1.163122696000001</v>
+        <v>-1.259348628000001</v>
       </c>
       <c r="P80">
-        <v>-2.779666104000002</v>
+        <v>-3.009629772000004</v>
       </c>
       <c r="Q80">
-        <v>0.7203338959999983</v>
+        <v>0.4903702279999962</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3063855757741632</v>
+        <v>0.31879441271579</v>
       </c>
       <c r="T80">
-        <v>4.031175981082171</v>
+        <v>4.223136742086084</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2492847796622043</v>
+        <v>0.2461292761221764</v>
       </c>
       <c r="W80">
-        <v>0.1102049943455884</v>
+        <v>0.1106682222652645</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8450331513973027</v>
+        <v>0.8343365292277165</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1543747222598749</v>
+        <v>0.1553847222598749</v>
       </c>
       <c r="C81">
-        <v>-17.49070022878334</v>
+        <v>-20.83387634015369</v>
       </c>
       <c r="D81">
-        <v>121.6472997712167</v>
+        <v>120.5261236598463</v>
       </c>
       <c r="E81">
-        <v>174.338</v>
+        <v>176.56</v>
       </c>
       <c r="F81">
-        <v>175.538</v>
+        <v>177.76</v>
       </c>
       <c r="G81">
         <v>36.4</v>
@@ -7929,37 +7929,37 @@
         <v>21.5</v>
       </c>
       <c r="M81">
-        <v>25.76897840000001</v>
+        <v>26.095168</v>
       </c>
       <c r="N81">
-        <v>-4.268978400000005</v>
+        <v>-4.595168000000001</v>
       </c>
       <c r="O81">
-        <v>-1.259348628000001</v>
+        <v>-1.35557456</v>
       </c>
       <c r="P81">
-        <v>-3.009629772000004</v>
+        <v>-3.239593440000001</v>
       </c>
       <c r="Q81">
-        <v>0.4903702279999962</v>
+        <v>0.260406559999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.31879441271579</v>
+        <v>0.3324441333515796</v>
       </c>
       <c r="T81">
-        <v>4.223136742086084</v>
+        <v>4.434293579190389</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2461292761221764</v>
+        <v>0.2430526601706492</v>
       </c>
       <c r="W81">
-        <v>0.1106682222652645</v>
+        <v>0.1111198694869487</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8343365292277165</v>
+        <v>0.8239073226123702</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1553847222598749</v>
+        <v>0.1563947222598749</v>
       </c>
       <c r="C82">
-        <v>-20.83387634015369</v>
+        <v>-24.15657429760597</v>
       </c>
       <c r="D82">
-        <v>120.5261236598463</v>
+        <v>119.425425702394</v>
       </c>
       <c r="E82">
-        <v>176.56</v>
+        <v>178.782</v>
       </c>
       <c r="F82">
-        <v>177.76</v>
+        <v>179.982</v>
       </c>
       <c r="G82">
         <v>36.4</v>
@@ -8011,37 +8011,37 @@
         <v>21.5</v>
       </c>
       <c r="M82">
-        <v>26.095168</v>
+        <v>26.4213576</v>
       </c>
       <c r="N82">
-        <v>-4.595168000000001</v>
+        <v>-4.921357600000004</v>
       </c>
       <c r="O82">
-        <v>-1.35557456</v>
+        <v>-1.451800492000001</v>
       </c>
       <c r="P82">
-        <v>-3.239593440000001</v>
+        <v>-3.469557108000003</v>
       </c>
       <c r="Q82">
-        <v>0.260406559999999</v>
+        <v>0.03044289199999728</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3324441333515796</v>
+        <v>0.3475306666858732</v>
       </c>
       <c r="T82">
-        <v>4.434293579190389</v>
+        <v>4.667677451779356</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2430526601706492</v>
+        <v>0.2400520100450856</v>
       </c>
       <c r="W82">
-        <v>0.1111198694869487</v>
+        <v>0.1115603649253814</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8239073226123702</v>
+        <v>0.8137356272714766</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1563947222598749</v>
+        <v>0.1574047222598748</v>
       </c>
       <c r="C83">
-        <v>-24.15657429760597</v>
+        <v>-27.45935007050338</v>
       </c>
       <c r="D83">
-        <v>119.425425702394</v>
+        <v>118.3446499294966</v>
       </c>
       <c r="E83">
-        <v>178.782</v>
+        <v>181.004</v>
       </c>
       <c r="F83">
-        <v>179.982</v>
+        <v>182.204</v>
       </c>
       <c r="G83">
         <v>36.4</v>
@@ -8093,37 +8093,37 @@
         <v>21.5</v>
       </c>
       <c r="M83">
-        <v>26.4213576</v>
+        <v>26.7475472</v>
       </c>
       <c r="N83">
-        <v>-4.921357600000004</v>
+        <v>-5.247547200000003</v>
       </c>
       <c r="O83">
-        <v>-1.451800492000001</v>
+        <v>-1.548026424000001</v>
       </c>
       <c r="P83">
-        <v>-3.469557108000003</v>
+        <v>-3.699520776000003</v>
       </c>
       <c r="Q83">
-        <v>0.03044289199999728</v>
+        <v>-0.1995207760000026</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3475306666858732</v>
+        <v>0.3642934815017551</v>
       </c>
       <c r="T83">
-        <v>4.667677451779356</v>
+        <v>4.926992865767099</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2400520100450856</v>
+        <v>0.2371245465079504</v>
       </c>
       <c r="W83">
-        <v>0.1115603649253814</v>
+        <v>0.1119901165726329</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8137356272714766</v>
+        <v>0.8038120220608489</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1574047222598748</v>
+        <v>0.2069560397528418</v>
       </c>
       <c r="C84">
-        <v>-27.45935007050338</v>
+        <v>-66.06927156102952</v>
       </c>
       <c r="D84">
-        <v>118.3446499294966</v>
+        <v>81.9567284389705</v>
       </c>
       <c r="E84">
-        <v>181.004</v>
+        <v>183.226</v>
       </c>
       <c r="F84">
-        <v>182.204</v>
+        <v>184.426</v>
       </c>
       <c r="G84">
         <v>36.4</v>
@@ -8175,45 +8175,45 @@
         <v>21.5</v>
       </c>
       <c r="M84">
-        <v>26.7475472</v>
+        <v>37.03274080000001</v>
       </c>
       <c r="N84">
-        <v>-5.247547200000003</v>
+        <v>-15.53274080000001</v>
       </c>
       <c r="O84">
-        <v>-1.548026424000001</v>
+        <v>-4.582158536000001</v>
       </c>
       <c r="P84">
-        <v>-3.699520776000003</v>
+        <v>-10.950582264</v>
       </c>
       <c r="Q84">
-        <v>-0.1995207760000026</v>
+        <v>-7.450582264000005</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3642934815017551</v>
+        <v>0.4049184950781341</v>
       </c>
       <c r="T84">
-        <v>4.926992865767099</v>
+        <v>5.555448905491128</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.2371245465079504</v>
+        <v>0.1712673667405141</v>
       </c>
       <c r="W84">
-        <v>0.1119901165726329</v>
+        <v>0.1664095127585048</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8038120220608489</v>
+        <v>0.5805673448830986</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2069560397528418</v>
+        <v>0.2085060397528418</v>
       </c>
       <c r="C85">
-        <v>-66.06927156102952</v>
+        <v>-69.07202271982712</v>
       </c>
       <c r="D85">
-        <v>81.9567284389705</v>
+        <v>81.17597728017287</v>
       </c>
       <c r="E85">
-        <v>183.226</v>
+        <v>185.448</v>
       </c>
       <c r="F85">
-        <v>184.426</v>
+        <v>186.648</v>
       </c>
       <c r="G85">
         <v>36.4</v>
@@ -8257,37 +8257,37 @@
         <v>21.5</v>
       </c>
       <c r="M85">
-        <v>37.03274080000001</v>
+        <v>37.4789184</v>
       </c>
       <c r="N85">
-        <v>-15.53274080000001</v>
+        <v>-15.9789184</v>
       </c>
       <c r="O85">
-        <v>-4.582158536000001</v>
+        <v>-4.713780927999999</v>
       </c>
       <c r="P85">
-        <v>-10.950582264</v>
+        <v>-11.265137472</v>
       </c>
       <c r="Q85">
-        <v>-7.450582264000005</v>
+        <v>-7.765137471999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4049184950781341</v>
+        <v>0.4273634010205175</v>
       </c>
       <c r="T85">
-        <v>5.555448905491128</v>
+        <v>5.902664462084322</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1712673667405141</v>
+        <v>0.1692284695174127</v>
       </c>
       <c r="W85">
-        <v>0.1664095127585048</v>
+        <v>0.1668189233209035</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5805673448830986</v>
+        <v>0.5736558288725857</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2085060397528417</v>
+        <v>0.2100560397528417</v>
       </c>
       <c r="C86">
-        <v>-69.07202271982709</v>
+        <v>-72.06003878215023</v>
       </c>
       <c r="D86">
-        <v>81.17597728017292</v>
+        <v>80.40996121784976</v>
       </c>
       <c r="E86">
-        <v>185.448</v>
+        <v>187.67</v>
       </c>
       <c r="F86">
-        <v>186.648</v>
+        <v>188.87</v>
       </c>
       <c r="G86">
         <v>36.4</v>
@@ -8339,37 +8339,37 @@
         <v>21.5</v>
       </c>
       <c r="M86">
-        <v>37.4789184</v>
+        <v>37.925096</v>
       </c>
       <c r="N86">
-        <v>-15.9789184</v>
+        <v>-16.425096</v>
       </c>
       <c r="O86">
-        <v>-4.713780927999999</v>
+        <v>-4.845403319999999</v>
       </c>
       <c r="P86">
-        <v>-11.265137472</v>
+        <v>-11.57969268</v>
       </c>
       <c r="Q86">
-        <v>-7.765137471999999</v>
+        <v>-8.079692679999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4273634010205172</v>
+        <v>0.4528009610885518</v>
       </c>
       <c r="T86">
-        <v>5.902664462084319</v>
+        <v>6.296175426223274</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1692284695174127</v>
+        <v>0.1672375463466197</v>
       </c>
       <c r="W86">
-        <v>0.1668189233209035</v>
+        <v>0.1672187006935988</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5736558288725857</v>
+        <v>0.5669069367682023</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2100560397528417</v>
+        <v>0.2116060397528417</v>
       </c>
       <c r="C87">
-        <v>-72.06003878215023</v>
+        <v>-75.03373299107926</v>
       </c>
       <c r="D87">
-        <v>80.40996121784976</v>
+        <v>79.65826700892073</v>
       </c>
       <c r="E87">
-        <v>187.67</v>
+        <v>189.892</v>
       </c>
       <c r="F87">
-        <v>188.87</v>
+        <v>191.092</v>
       </c>
       <c r="G87">
         <v>36.4</v>
@@ -8421,37 +8421,37 @@
         <v>21.5</v>
       </c>
       <c r="M87">
-        <v>37.925096</v>
+        <v>38.37127359999999</v>
       </c>
       <c r="N87">
-        <v>-16.425096</v>
+        <v>-16.87127359999999</v>
       </c>
       <c r="O87">
-        <v>-4.845403319999999</v>
+        <v>-4.977025711999998</v>
       </c>
       <c r="P87">
-        <v>-11.57969268</v>
+        <v>-11.894247888</v>
       </c>
       <c r="Q87">
-        <v>-8.079692679999997</v>
+        <v>-8.394247887999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4528009610885518</v>
+        <v>0.4818724583091625</v>
       </c>
       <c r="T87">
-        <v>6.296175426223274</v>
+        <v>6.745902242382078</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1672375463466197</v>
+        <v>0.1652929237146822</v>
       </c>
       <c r="W87">
-        <v>0.1672187006935988</v>
+        <v>0.1676091809180918</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5669069367682023</v>
+        <v>0.5603149956429907</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2116060397528417</v>
+        <v>0.2131560397528417</v>
       </c>
       <c r="C88">
-        <v>-75.03373299107926</v>
+        <v>-77.99350328037491</v>
       </c>
       <c r="D88">
-        <v>79.65826700892073</v>
+        <v>78.92049671962508</v>
       </c>
       <c r="E88">
-        <v>189.892</v>
+        <v>192.114</v>
       </c>
       <c r="F88">
-        <v>191.092</v>
+        <v>193.314</v>
       </c>
       <c r="G88">
         <v>36.4</v>
@@ -8503,37 +8503,37 @@
         <v>21.5</v>
       </c>
       <c r="M88">
-        <v>38.37127359999999</v>
+        <v>38.8174512</v>
       </c>
       <c r="N88">
-        <v>-16.87127359999999</v>
+        <v>-17.3174512</v>
       </c>
       <c r="O88">
-        <v>-4.977025711999998</v>
+        <v>-5.108648104</v>
       </c>
       <c r="P88">
-        <v>-11.894247888</v>
+        <v>-12.208803096</v>
       </c>
       <c r="Q88">
-        <v>-8.394247887999997</v>
+        <v>-8.708803096</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4818724583091625</v>
+        <v>0.5154164935637134</v>
       </c>
       <c r="T88">
-        <v>6.745902242382078</v>
+        <v>7.264817799488393</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1652929237146822</v>
+        <v>0.1633930050512951</v>
       </c>
       <c r="W88">
-        <v>0.1676091809180918</v>
+        <v>0.1679906845857</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5603149956429907</v>
+        <v>0.5538745933942206</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2131560397528417</v>
+        <v>0.2147060397528417</v>
       </c>
       <c r="C89">
-        <v>-77.99350328037491</v>
+        <v>-80.93973297692349</v>
       </c>
       <c r="D89">
-        <v>78.92049671962508</v>
+        <v>78.19626702307652</v>
       </c>
       <c r="E89">
-        <v>192.114</v>
+        <v>194.336</v>
       </c>
       <c r="F89">
-        <v>193.314</v>
+        <v>195.536</v>
       </c>
       <c r="G89">
         <v>36.4</v>
@@ -8585,37 +8585,37 @@
         <v>21.5</v>
       </c>
       <c r="M89">
-        <v>38.8174512</v>
+        <v>39.2636288</v>
       </c>
       <c r="N89">
-        <v>-17.3174512</v>
+        <v>-17.7636288</v>
       </c>
       <c r="O89">
-        <v>-5.108648104</v>
+        <v>-5.240270496</v>
       </c>
       <c r="P89">
-        <v>-12.208803096</v>
+        <v>-12.523358304</v>
       </c>
       <c r="Q89">
-        <v>-8.708803096</v>
+        <v>-9.023358303999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5154164935637134</v>
+        <v>0.5545512013606897</v>
       </c>
       <c r="T89">
-        <v>7.264817799488393</v>
+        <v>7.870219282779094</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1633930050512951</v>
+        <v>0.1615362663575304</v>
       </c>
       <c r="W89">
-        <v>0.1679906845857</v>
+        <v>0.1683635177154079</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5538745933942206</v>
+        <v>0.5475805639238318</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2147060397528417</v>
+        <v>0.2162560397528417</v>
       </c>
       <c r="C90">
-        <v>-80.93973297692349</v>
+        <v>-83.87279146485685</v>
       </c>
       <c r="D90">
-        <v>78.19626702307652</v>
+        <v>77.48520853514314</v>
       </c>
       <c r="E90">
-        <v>194.336</v>
+        <v>196.558</v>
       </c>
       <c r="F90">
-        <v>195.536</v>
+        <v>197.758</v>
       </c>
       <c r="G90">
         <v>36.4</v>
@@ -8667,37 +8667,37 @@
         <v>21.5</v>
       </c>
       <c r="M90">
-        <v>39.2636288</v>
+        <v>39.7098064</v>
       </c>
       <c r="N90">
-        <v>-17.7636288</v>
+        <v>-18.2098064</v>
       </c>
       <c r="O90">
-        <v>-5.240270496</v>
+        <v>-5.371892887999999</v>
       </c>
       <c r="P90">
-        <v>-12.523358304</v>
+        <v>-12.837913512</v>
       </c>
       <c r="Q90">
-        <v>-9.023358303999998</v>
+        <v>-9.337913512</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5545512013606897</v>
+        <v>0.6008013105752978</v>
       </c>
       <c r="T90">
-        <v>7.870219282779094</v>
+        <v>8.585693763031738</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1615362663575304</v>
+        <v>0.1597212521287941</v>
       </c>
       <c r="W90">
-        <v>0.1683635177154079</v>
+        <v>0.1687279725725382</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5475805639238318</v>
+        <v>0.541427973317946</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2162560397528417</v>
+        <v>0.2178060397528417</v>
       </c>
       <c r="C91">
-        <v>-83.87279146485685</v>
+        <v>-86.7930348137651</v>
       </c>
       <c r="D91">
-        <v>77.48520853514314</v>
+        <v>76.78696518623488</v>
       </c>
       <c r="E91">
-        <v>196.558</v>
+        <v>198.78</v>
       </c>
       <c r="F91">
-        <v>197.758</v>
+        <v>199.98</v>
       </c>
       <c r="G91">
         <v>36.4</v>
@@ -8749,37 +8749,37 @@
         <v>21.5</v>
       </c>
       <c r="M91">
-        <v>39.7098064</v>
+        <v>40.155984</v>
       </c>
       <c r="N91">
-        <v>-18.2098064</v>
+        <v>-18.655984</v>
       </c>
       <c r="O91">
-        <v>-5.371892887999999</v>
+        <v>-5.503515279999998</v>
       </c>
       <c r="P91">
-        <v>-12.837913512</v>
+        <v>-13.15246872</v>
       </c>
       <c r="Q91">
-        <v>-9.337913512</v>
+        <v>-9.652468719999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6008013105752978</v>
+        <v>0.6563014416328277</v>
       </c>
       <c r="T91">
-        <v>8.585693763031738</v>
+        <v>9.444263139334913</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1597212521287941</v>
+        <v>0.1579465715495852</v>
       </c>
       <c r="W91">
-        <v>0.1687279725725382</v>
+        <v>0.1690843284328433</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.541427973317946</v>
+        <v>0.5354121069477467</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2178060397528417</v>
+        <v>0.2193560397528417</v>
       </c>
       <c r="C92">
-        <v>-86.7930348137651</v>
+        <v>-89.70080637324619</v>
       </c>
       <c r="D92">
-        <v>76.78696518623488</v>
+        <v>76.1011936267538</v>
       </c>
       <c r="E92">
-        <v>198.78</v>
+        <v>201.002</v>
       </c>
       <c r="F92">
-        <v>199.98</v>
+        <v>202.202</v>
       </c>
       <c r="G92">
         <v>36.4</v>
@@ -8831,37 +8831,37 @@
         <v>21.5</v>
       </c>
       <c r="M92">
-        <v>40.155984</v>
+        <v>40.6021616</v>
       </c>
       <c r="N92">
-        <v>-18.655984</v>
+        <v>-19.1021616</v>
       </c>
       <c r="O92">
-        <v>-5.503515279999998</v>
+        <v>-5.635137672000001</v>
       </c>
       <c r="P92">
-        <v>-13.15246872</v>
+        <v>-13.467023928</v>
       </c>
       <c r="Q92">
-        <v>-9.652468719999998</v>
+        <v>-9.967023928000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6563014416328277</v>
+        <v>0.7241349351475865</v>
       </c>
       <c r="T92">
-        <v>9.444263139334913</v>
+        <v>10.49362571037213</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1579465715495852</v>
+        <v>0.1562108949391502</v>
       </c>
       <c r="W92">
-        <v>0.1690843284328433</v>
+        <v>0.1694328522962187</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5354121069477467</v>
+        <v>0.5295284574208482</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2193560397528417</v>
+        <v>0.2209060397528417</v>
       </c>
       <c r="C93">
-        <v>-89.70080637324619</v>
+        <v>-92.59643733587868</v>
       </c>
       <c r="D93">
-        <v>76.1011936267538</v>
+        <v>75.42756266412134</v>
       </c>
       <c r="E93">
-        <v>201.002</v>
+        <v>203.224</v>
       </c>
       <c r="F93">
-        <v>202.202</v>
+        <v>204.424</v>
       </c>
       <c r="G93">
         <v>36.4</v>
@@ -8913,37 +8913,37 @@
         <v>21.5</v>
       </c>
       <c r="M93">
-        <v>40.6021616</v>
+        <v>41.0483392</v>
       </c>
       <c r="N93">
-        <v>-19.1021616</v>
+        <v>-19.5483392</v>
       </c>
       <c r="O93">
-        <v>-5.635137672000001</v>
+        <v>-5.766760064</v>
       </c>
       <c r="P93">
-        <v>-13.467023928</v>
+        <v>-13.781579136</v>
       </c>
       <c r="Q93">
-        <v>-9.967023928000001</v>
+        <v>-10.281579136</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7241349351475865</v>
+        <v>0.8089268020410348</v>
       </c>
       <c r="T93">
-        <v>10.49362571037213</v>
+        <v>11.80532892416864</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1562108949391502</v>
+        <v>0.1545129504289421</v>
       </c>
       <c r="W93">
-        <v>0.1694328522962187</v>
+        <v>0.1697737995538684</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5295284574208482</v>
+        <v>0.5237727133184478</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2209060397528417</v>
+        <v>0.2224560397528417</v>
       </c>
       <c r="C94">
-        <v>-92.59643733587868</v>
+        <v>-95.48024727055716</v>
       </c>
       <c r="D94">
-        <v>75.42756266412134</v>
+        <v>74.76575272944284</v>
       </c>
       <c r="E94">
-        <v>203.224</v>
+        <v>205.446</v>
       </c>
       <c r="F94">
-        <v>204.424</v>
+        <v>206.646</v>
       </c>
       <c r="G94">
         <v>36.4</v>
@@ -8995,37 +8995,37 @@
         <v>21.5</v>
       </c>
       <c r="M94">
-        <v>41.0483392</v>
+        <v>41.4945168</v>
       </c>
       <c r="N94">
-        <v>-19.5483392</v>
+        <v>-19.9945168</v>
       </c>
       <c r="O94">
-        <v>-5.766760064</v>
+        <v>-5.898382455999999</v>
       </c>
       <c r="P94">
-        <v>-13.781579136</v>
+        <v>-14.096134344</v>
       </c>
       <c r="Q94">
-        <v>-10.281579136</v>
+        <v>-10.596134344</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8089268020410348</v>
+        <v>0.9179449166183257</v>
       </c>
       <c r="T94">
-        <v>11.80532892416864</v>
+        <v>13.49180448476417</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1545129504289421</v>
+        <v>0.1528515208544373</v>
       </c>
       <c r="W94">
-        <v>0.1697737995538684</v>
+        <v>0.170107414612429</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5237727133184478</v>
+        <v>0.5181407486591096</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2224560397528417</v>
+        <v>0.2240060397528417</v>
       </c>
       <c r="C95">
-        <v>-95.48024727055716</v>
+        <v>-98.35254462799443</v>
       </c>
       <c r="D95">
-        <v>74.76575272944284</v>
+        <v>74.11545537200556</v>
       </c>
       <c r="E95">
-        <v>205.446</v>
+        <v>207.668</v>
       </c>
       <c r="F95">
-        <v>206.646</v>
+        <v>208.868</v>
       </c>
       <c r="G95">
         <v>36.4</v>
@@ -9077,37 +9077,37 @@
         <v>21.5</v>
       </c>
       <c r="M95">
-        <v>41.4945168</v>
+        <v>41.9406944</v>
       </c>
       <c r="N95">
-        <v>-19.9945168</v>
+        <v>-20.4406944</v>
       </c>
       <c r="O95">
-        <v>-5.898382455999999</v>
+        <v>-6.030004847999999</v>
       </c>
       <c r="P95">
-        <v>-14.096134344</v>
+        <v>-14.410689552</v>
       </c>
       <c r="Q95">
-        <v>-10.596134344</v>
+        <v>-10.910689552</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9179449166183257</v>
+        <v>1.06330240272138</v>
       </c>
       <c r="T95">
-        <v>13.49180448476417</v>
+        <v>15.7404385655582</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1528515208544373</v>
+        <v>0.1512254408453476</v>
       </c>
       <c r="W95">
-        <v>0.170107414612429</v>
+        <v>0.1704339314782542</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5181407486591096</v>
+        <v>0.5126286130350766</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2240060397528417</v>
+        <v>0.2255560397528417</v>
       </c>
       <c r="C96">
-        <v>-98.35254462799443</v>
+        <v>-101.2136272200707</v>
       </c>
       <c r="D96">
-        <v>74.11545537200556</v>
+        <v>73.47637277992931</v>
       </c>
       <c r="E96">
-        <v>207.668</v>
+        <v>209.89</v>
       </c>
       <c r="F96">
-        <v>208.868</v>
+        <v>211.09</v>
       </c>
       <c r="G96">
         <v>36.4</v>
@@ -9159,37 +9159,37 @@
         <v>21.5</v>
       </c>
       <c r="M96">
-        <v>41.9406944</v>
+        <v>42.386872</v>
       </c>
       <c r="N96">
-        <v>-20.4406944</v>
+        <v>-20.886872</v>
       </c>
       <c r="O96">
-        <v>-6.030004847999999</v>
+        <v>-6.161627240000001</v>
       </c>
       <c r="P96">
-        <v>-14.410689552</v>
+        <v>-14.72524476</v>
       </c>
       <c r="Q96">
-        <v>-10.910689552</v>
+        <v>-11.22524476</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.06330240272138</v>
+        <v>1.266802883265657</v>
       </c>
       <c r="T96">
-        <v>15.7404385655582</v>
+        <v>18.88852627866985</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1512254408453476</v>
+        <v>0.1496335940996071</v>
       </c>
       <c r="W96">
-        <v>0.1704339314782542</v>
+        <v>0.1707535743047989</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5126286130350766</v>
+        <v>0.5072325223715493</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2255560397528417</v>
+        <v>0.2271060397528417</v>
       </c>
       <c r="C97">
-        <v>-101.2136272200707</v>
+        <v>-104.0637826745947</v>
       </c>
       <c r="D97">
-        <v>73.47637277992931</v>
+        <v>72.84821732540533</v>
       </c>
       <c r="E97">
-        <v>209.89</v>
+        <v>212.112</v>
       </c>
       <c r="F97">
-        <v>211.09</v>
+        <v>213.312</v>
       </c>
       <c r="G97">
         <v>36.4</v>
@@ -9241,37 +9241,37 @@
         <v>21.5</v>
       </c>
       <c r="M97">
-        <v>42.386872</v>
+        <v>42.8330496</v>
       </c>
       <c r="N97">
-        <v>-20.886872</v>
+        <v>-21.3330496</v>
       </c>
       <c r="O97">
-        <v>-6.161627240000001</v>
+        <v>-6.293249632</v>
       </c>
       <c r="P97">
-        <v>-14.72524476</v>
+        <v>-15.039799968</v>
       </c>
       <c r="Q97">
-        <v>-11.22524476</v>
+        <v>-11.539799968</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.266802883265657</v>
+        <v>1.572053604082072</v>
       </c>
       <c r="T97">
-        <v>18.88852627866985</v>
+        <v>23.61065784833732</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1496335940996071</v>
+        <v>0.1480749108277361</v>
       </c>
       <c r="W97">
-        <v>0.1707535743047989</v>
+        <v>0.1710665579057906</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5072325223715493</v>
+        <v>0.5019488502635123</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2271060397528417</v>
+        <v>0.2641076363097845</v>
       </c>
       <c r="C98">
-        <v>-104.0637826745946</v>
+        <v>-118.6330390185832</v>
       </c>
       <c r="D98">
-        <v>72.84821732540533</v>
+        <v>60.50096098141675</v>
       </c>
       <c r="E98">
-        <v>212.112</v>
+        <v>214.334</v>
       </c>
       <c r="F98">
-        <v>213.312</v>
+        <v>215.534</v>
       </c>
       <c r="G98">
         <v>36.4</v>
@@ -9323,45 +9323,45 @@
         <v>21.5</v>
       </c>
       <c r="M98">
-        <v>42.8330496</v>
+        <v>50.8229172</v>
       </c>
       <c r="N98">
-        <v>-21.3330496</v>
+        <v>-29.3229172</v>
       </c>
       <c r="O98">
-        <v>-6.293249631999998</v>
+        <v>-8.650260573999999</v>
       </c>
       <c r="P98">
-        <v>-15.039799968</v>
+        <v>-20.672656626</v>
       </c>
       <c r="Q98">
-        <v>-11.539799968</v>
+        <v>-17.172656626</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.572053604082068</v>
+        <v>2.130858024007516</v>
       </c>
       <c r="T98">
-        <v>23.61065784833726</v>
+        <v>32.25518450348212</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1480749108277362</v>
+        <v>0.1247960634577663</v>
       </c>
       <c r="W98">
-        <v>0.1710665579057906</v>
+        <v>0.2063730882366587</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5019488502635124</v>
+        <v>0.4230375032466652</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2641076363097845</v>
+        <v>0.2660076363097845</v>
       </c>
       <c r="C99">
-        <v>-118.6330390185832</v>
+        <v>-121.3770546388907</v>
       </c>
       <c r="D99">
-        <v>60.50096098141675</v>
+        <v>59.9789453611093</v>
       </c>
       <c r="E99">
-        <v>214.334</v>
+        <v>216.556</v>
       </c>
       <c r="F99">
-        <v>215.534</v>
+        <v>217.756</v>
       </c>
       <c r="G99">
         <v>36.4</v>
@@ -9405,37 +9405,37 @@
         <v>21.5</v>
       </c>
       <c r="M99">
-        <v>50.8229172</v>
+        <v>51.3468648</v>
       </c>
       <c r="N99">
-        <v>-29.3229172</v>
+        <v>-29.8468648</v>
       </c>
       <c r="O99">
-        <v>-8.650260573999999</v>
+        <v>-8.804825116</v>
       </c>
       <c r="P99">
-        <v>-20.672656626</v>
+        <v>-21.042039684</v>
       </c>
       <c r="Q99">
-        <v>-17.172656626</v>
+        <v>-17.542039684</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.130858024007516</v>
+        <v>3.173387036011274</v>
       </c>
       <c r="T99">
-        <v>32.25518450348212</v>
+        <v>48.38277675522317</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1247960634577663</v>
+        <v>0.1235226342388095</v>
       </c>
       <c r="W99">
-        <v>0.2063730882366587</v>
+        <v>0.2066733628464887</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4230375032466652</v>
+        <v>0.4187207940298626</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2660076363097845</v>
+        <v>0.2679076363097845</v>
       </c>
       <c r="C100">
-        <v>-121.3770546388907</v>
+        <v>-124.1121391869031</v>
       </c>
       <c r="D100">
-        <v>59.9789453611093</v>
+        <v>59.46586081309691</v>
       </c>
       <c r="E100">
-        <v>216.556</v>
+        <v>218.778</v>
       </c>
       <c r="F100">
-        <v>217.756</v>
+        <v>219.978</v>
       </c>
       <c r="G100">
         <v>36.4</v>
@@ -9487,37 +9487,37 @@
         <v>21.5</v>
       </c>
       <c r="M100">
-        <v>51.3468648</v>
+        <v>51.8708124</v>
       </c>
       <c r="N100">
-        <v>-29.8468648</v>
+        <v>-30.3708124</v>
       </c>
       <c r="O100">
-        <v>-8.804825116</v>
+        <v>-8.959389657999999</v>
       </c>
       <c r="P100">
-        <v>-21.042039684</v>
+        <v>-21.411422742</v>
       </c>
       <c r="Q100">
-        <v>-17.542039684</v>
+        <v>-17.911422742</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.173387036011274</v>
+        <v>6.300974072022549</v>
       </c>
       <c r="T100">
-        <v>48.38277675522317</v>
+        <v>96.76555351044635</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1235226342388095</v>
+        <v>0.1222749308626599</v>
       </c>
       <c r="W100">
-        <v>0.2066733628464887</v>
+        <v>0.2069675713025848</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4187207940298626</v>
+        <v>0.4144912910598639</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2679076363097845</v>
-      </c>
-      <c r="C101">
-        <v>-124.1121391869031</v>
-      </c>
-      <c r="D101">
-        <v>59.46586081309691</v>
-      </c>
-      <c r="E101">
-        <v>218.778</v>
-      </c>
-      <c r="F101">
-        <v>219.978</v>
-      </c>
-      <c r="G101">
-        <v>36.4</v>
-      </c>
-      <c r="H101">
-        <v>221</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>25</v>
-      </c>
-      <c r="K101">
-        <v>3.5</v>
-      </c>
-      <c r="L101">
-        <v>21.5</v>
-      </c>
-      <c r="M101">
-        <v>51.8708124</v>
-      </c>
-      <c r="N101">
-        <v>-30.3708124</v>
-      </c>
-      <c r="O101">
-        <v>-8.959389657999999</v>
-      </c>
-      <c r="P101">
-        <v>-21.411422742</v>
-      </c>
-      <c r="Q101">
-        <v>-17.911422742</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.300974072022549</v>
-      </c>
-      <c r="T101">
-        <v>96.76555351044635</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1222749308626599</v>
-      </c>
-      <c r="W101">
-        <v>0.2069675713025848</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4144912910598639</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
